--- a/codex_nuevoadmin_check.xlsx
+++ b/codex_nuevoadmin_check.xlsx
@@ -52,7 +52,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO51"/>
+  <dimension ref="A1:AO61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
@@ -268,10 +268,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>505988.89</v>
+        <v>920293.44</v>
       </c>
       <c r="C2">
-        <v>49128297</v>
+        <v>65438535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -287,25 +287,25 @@
         <v>42239.41</v>
       </c>
       <c r="G2">
-        <v>8.35</v>
+        <v>4.59</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J2">
         <v>4212744</v>
       </c>
       <c r="K2">
-        <v>8.57</v>
+        <v>6.44</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2">
         <v>4</v>
@@ -333,7 +333,7 @@
         <v>5.59</v>
       </c>
       <c r="U2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -349,13 +349,13 @@
         <v>8775.0</v>
       </c>
       <c r="Y2">
-        <v>1.73</v>
+        <v>0.95</v>
       </c>
       <c r="Z2">
         <v>20.77</v>
       </c>
       <c r="AA2">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AB2">
         <v>3</v>
@@ -364,13 +364,13 @@
         <v>770554</v>
       </c>
       <c r="AD2">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AE2">
         <v>18.29</v>
       </c>
       <c r="AF2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AG2">
         <v>3</v>
@@ -400,6 +400,9 @@
       <c r="AN2">
         <v>26.57</v>
       </c>
+      <c r="AO2">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="V3" t="inlineStr">
@@ -416,13 +419,13 @@
         <v>12647.0</v>
       </c>
       <c r="Y3">
-        <v>2.5</v>
+        <v>1.37</v>
       </c>
       <c r="Z3">
         <v>29.94</v>
       </c>
       <c r="AA3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB3">
         <v>2</v>
@@ -431,13 +434,13 @@
         <v>945797</v>
       </c>
       <c r="AD3">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="AE3">
         <v>22.45</v>
       </c>
       <c r="AF3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AG3">
         <v>2</v>
@@ -467,6 +470,9 @@
       <c r="AN3">
         <v>24.88</v>
       </c>
+      <c r="AO3">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
       <c r="V4" t="inlineStr">
@@ -483,13 +489,13 @@
         <v>13496.0</v>
       </c>
       <c r="Y4">
-        <v>2.67</v>
+        <v>1.47</v>
       </c>
       <c r="Z4">
         <v>31.95</v>
       </c>
       <c r="AA4">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AB4">
         <v>1</v>
@@ -498,13 +504,13 @@
         <v>618143</v>
       </c>
       <c r="AD4">
-        <v>1.26</v>
+        <v>0.94</v>
       </c>
       <c r="AE4">
         <v>14.67</v>
       </c>
       <c r="AF4">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="AG4">
         <v>4</v>
@@ -534,6 +540,9 @@
       <c r="AN4">
         <v>18.14</v>
       </c>
+      <c r="AO4">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="V5" t="inlineStr">
@@ -550,13 +559,13 @@
         <v>7321.41</v>
       </c>
       <c r="Y5">
-        <v>1.45</v>
+        <v>0.8</v>
       </c>
       <c r="Z5">
         <v>17.33</v>
       </c>
       <c r="AA5">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AB5">
         <v>4</v>
@@ -565,13 +574,13 @@
         <v>1878250</v>
       </c>
       <c r="AD5">
-        <v>3.82</v>
+        <v>2.87</v>
       </c>
       <c r="AE5">
         <v>44.58</v>
       </c>
       <c r="AF5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>1</v>
@@ -601,6 +610,9 @@
       <c r="AN5">
         <v>31.79</v>
       </c>
+      <c r="AO5">
+        <v>14</v>
+      </c>
     </row>
     <row r="6">
       <c r="D6" t="inlineStr">
@@ -617,25 +629,25 @@
         <v>45390.48</v>
       </c>
       <c r="G6">
-        <v>8.97</v>
+        <v>4.93</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>4634603</v>
       </c>
       <c r="K6">
-        <v>9.43</v>
+        <v>7.08</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>4</v>
@@ -663,7 +675,7 @@
         <v>14.86</v>
       </c>
       <c r="U6">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -679,13 +691,13 @@
         <v>7455.48</v>
       </c>
       <c r="Y6">
-        <v>1.47</v>
+        <v>0.81</v>
       </c>
       <c r="Z6">
         <v>16.43</v>
       </c>
       <c r="AA6">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="AB6">
         <v>4</v>
@@ -694,13 +706,13 @@
         <v>1344987</v>
       </c>
       <c r="AD6">
-        <v>2.74</v>
+        <v>2.06</v>
       </c>
       <c r="AE6">
         <v>29.02</v>
       </c>
       <c r="AF6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AG6">
         <v>2</v>
@@ -730,6 +742,9 @@
       <c r="AN6">
         <v>15.99</v>
       </c>
+      <c r="AO6">
+        <v>10</v>
+      </c>
     </row>
     <row r="7">
       <c r="V7" t="inlineStr">
@@ -746,13 +761,13 @@
         <v>13771.0</v>
       </c>
       <c r="Y7">
-        <v>2.72</v>
+        <v>1.5</v>
       </c>
       <c r="Z7">
         <v>30.34</v>
       </c>
       <c r="AA7">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AB7">
         <v>2</v>
@@ -761,13 +776,13 @@
         <v>773163</v>
       </c>
       <c r="AD7">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AE7">
         <v>16.68</v>
       </c>
       <c r="AF7">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AG7">
         <v>3</v>
@@ -797,6 +812,9 @@
       <c r="AN7">
         <v>41.93</v>
       </c>
+      <c r="AO7">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="V8" t="inlineStr">
@@ -813,13 +831,13 @@
         <v>10128.0</v>
       </c>
       <c r="Y8">
-        <v>2.0</v>
+        <v>1.1</v>
       </c>
       <c r="Z8">
         <v>22.31</v>
       </c>
       <c r="AA8">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AB8">
         <v>3</v>
@@ -828,13 +846,13 @@
         <v>538789</v>
       </c>
       <c r="AD8">
-        <v>1.1</v>
+        <v>0.82</v>
       </c>
       <c r="AE8">
         <v>11.63</v>
       </c>
       <c r="AF8">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="AG8">
         <v>4</v>
@@ -864,6 +882,9 @@
       <c r="AN8">
         <v>26.68</v>
       </c>
+      <c r="AO8">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="V9" t="inlineStr">
@@ -880,13 +901,13 @@
         <v>14036.0</v>
       </c>
       <c r="Y9">
-        <v>2.77</v>
+        <v>1.53</v>
       </c>
       <c r="Z9">
         <v>30.92</v>
       </c>
       <c r="AA9">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AB9">
         <v>1</v>
@@ -895,13 +916,13 @@
         <v>1977664</v>
       </c>
       <c r="AD9">
-        <v>4.03</v>
+        <v>3.02</v>
       </c>
       <c r="AE9">
         <v>42.67</v>
       </c>
       <c r="AF9">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AG9">
         <v>1</v>
@@ -931,6 +952,9 @@
       <c r="AN9">
         <v>34.82</v>
       </c>
+      <c r="AO9">
+        <v>15</v>
+      </c>
     </row>
     <row r="10">
       <c r="D10" t="inlineStr">
@@ -940,60 +964,60 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aragón</t>
+          <t>África Occidental</t>
         </is>
       </c>
       <c r="F10">
-        <v>47721.0</v>
+        <v>267502.0</v>
       </c>
       <c r="G10">
-        <v>9.43</v>
+        <v>29.07</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>1364621</v>
+        <v>709476</v>
       </c>
       <c r="K10">
-        <v>2.78</v>
+        <v>1.08</v>
       </c>
       <c r="L10">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M10">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Sidi Ifni</t>
         </is>
       </c>
       <c r="P10">
-        <v>699007</v>
+        <v>104601</v>
       </c>
       <c r="Q10">
-        <v>51.22</v>
+        <v>14.74</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Sidi Ifni</t>
         </is>
       </c>
       <c r="S10">
-        <v>699007</v>
+        <v>104601</v>
       </c>
       <c r="T10">
-        <v>51.22</v>
+        <v>14.74</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1002,63 +1026,66 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Ifni</t>
         </is>
       </c>
       <c r="X10">
-        <v>15636.0</v>
+        <v>1502.0</v>
       </c>
       <c r="Y10">
-        <v>3.09</v>
+        <v>0.16</v>
       </c>
       <c r="Z10">
-        <v>32.77</v>
+        <v>0.56</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="AB10">
         <v>2</v>
       </c>
       <c r="AC10">
-        <v>230087</v>
+        <v>38483</v>
       </c>
       <c r="AD10">
-        <v>0.47</v>
+        <v>0.06</v>
       </c>
       <c r="AE10">
-        <v>16.86</v>
+        <v>5.42</v>
       </c>
       <c r="AF10">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="AG10">
         <v>2</v>
       </c>
       <c r="AH10">
-        <v>202</v>
+        <v>4</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Sidi Ifni</t>
         </is>
       </c>
       <c r="AJ10">
-        <v>55033</v>
+        <v>22696</v>
       </c>
       <c r="AK10">
-        <v>23.92</v>
+        <v>58.98</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Sidi Ifni</t>
         </is>
       </c>
       <c r="AM10">
-        <v>55033</v>
+        <v>22696</v>
       </c>
       <c r="AN10">
-        <v>23.92</v>
+        <v>58.98</v>
+      </c>
+      <c r="AO10">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1069,388 +1096,335 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Sahara</t>
+        </is>
+      </c>
+      <c r="X11">
+        <v>266000.0</v>
+      </c>
+      <c r="Y11">
+        <v>28.9</v>
+      </c>
+      <c r="Z11">
+        <v>99.44</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>1</v>
+      </c>
+      <c r="AC11">
+        <v>670993</v>
+      </c>
+      <c r="AD11">
+        <v>1.03</v>
+      </c>
+      <c r="AE11">
+        <v>94.58</v>
+      </c>
+      <c r="AF11">
+        <v>32</v>
+      </c>
+      <c r="AG11">
+        <v>1</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Laâyoune</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>295555</v>
+      </c>
+      <c r="AK11">
+        <v>44.05</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Laâyoune</t>
+        </is>
+      </c>
+      <c r="AM11">
+        <v>295555</v>
+      </c>
+      <c r="AN11">
+        <v>44.05</v>
+      </c>
+      <c r="AO11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>47721.0</v>
+      </c>
+      <c r="G12">
+        <v>5.19</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>1364621</v>
+      </c>
+      <c r="K12">
+        <v>2.09</v>
+      </c>
+      <c r="L12">
+        <v>13</v>
+      </c>
+      <c r="M12">
+        <v>13</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="P12">
+        <v>699007</v>
+      </c>
+      <c r="Q12">
+        <v>51.22</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="S12">
+        <v>699007</v>
+      </c>
+      <c r="T12">
+        <v>51.22</v>
+      </c>
+      <c r="U12">
+        <v>11</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="X12">
+        <v>15636.0</v>
+      </c>
+      <c r="Y12">
+        <v>1.7</v>
+      </c>
+      <c r="Z12">
+        <v>32.77</v>
+      </c>
+      <c r="AA12">
+        <v>11</v>
+      </c>
+      <c r="AB12">
+        <v>2</v>
+      </c>
+      <c r="AC12">
+        <v>230087</v>
+      </c>
+      <c r="AD12">
+        <v>0.35</v>
+      </c>
+      <c r="AE12">
+        <v>16.86</v>
+      </c>
+      <c r="AF12">
+        <v>52</v>
+      </c>
+      <c r="AG12">
+        <v>2</v>
+      </c>
+      <c r="AH12">
+        <v>202</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>55033</v>
+      </c>
+      <c r="AK12">
+        <v>23.92</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="AM12">
+        <v>55033</v>
+      </c>
+      <c r="AN12">
+        <v>23.92</v>
+      </c>
+      <c r="AO12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>Teruel</t>
         </is>
       </c>
-      <c r="X11">
+      <c r="X13">
         <v>14810.0</v>
       </c>
-      <c r="Y11">
-        <v>2.93</v>
-      </c>
-      <c r="Z11">
+      <c r="Y13">
+        <v>1.61</v>
+      </c>
+      <c r="Z13">
         <v>31.03</v>
       </c>
-      <c r="AA11">
-        <v>10</v>
-      </c>
-      <c r="AB11">
+      <c r="AA13">
+        <v>15</v>
+      </c>
+      <c r="AB13">
         <v>3</v>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <v>136091</v>
       </c>
-      <c r="AD11">
-        <v>0.28</v>
-      </c>
-      <c r="AE11">
+      <c r="AD13">
+        <v>0.21</v>
+      </c>
+      <c r="AE13">
         <v>9.97</v>
       </c>
-      <c r="AF11">
-        <v>49</v>
-      </c>
-      <c r="AG11">
+      <c r="AF13">
+        <v>58</v>
+      </c>
+      <c r="AG13">
         <v>3</v>
       </c>
-      <c r="AH11">
+      <c r="AH13">
         <v>236</v>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>Teruel</t>
         </is>
       </c>
-      <c r="AJ11">
+      <c r="AJ13">
         <v>36521</v>
       </c>
-      <c r="AK11">
+      <c r="AK13">
         <v>26.84</v>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AL13" t="inlineStr">
         <is>
           <t>Teruel</t>
         </is>
       </c>
-      <c r="AM11">
+      <c r="AM13">
         <v>36521</v>
       </c>
-      <c r="AN11">
+      <c r="AN13">
         <v>26.84</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="AO13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>Zaragoza</t>
         </is>
       </c>
-      <c r="X12">
+      <c r="X14">
         <v>17275.0</v>
       </c>
-      <c r="Y12">
-        <v>3.41</v>
-      </c>
-      <c r="Z12">
+      <c r="Y14">
+        <v>1.88</v>
+      </c>
+      <c r="Z14">
         <v>36.2</v>
       </c>
-      <c r="AA12">
-        <v>4</v>
-      </c>
-      <c r="AB12">
-        <v>1</v>
-      </c>
-      <c r="AC12">
-        <v>998443</v>
-      </c>
-      <c r="AD12">
-        <v>2.03</v>
-      </c>
-      <c r="AE12">
-        <v>73.17</v>
-      </c>
-      <c r="AF12">
-        <v>15</v>
-      </c>
-      <c r="AG12">
-        <v>1</v>
-      </c>
-      <c r="AH12">
-        <v>293</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Zaragoza</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>699007</v>
-      </c>
-      <c r="AK12">
-        <v>70.01</v>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Zaragoza</t>
-        </is>
-      </c>
-      <c r="AM12">
-        <v>699007</v>
-      </c>
-      <c r="AN12">
-        <v>70.01</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Asturias</t>
-        </is>
-      </c>
-      <c r="F13">
-        <v>10604.0</v>
-      </c>
-      <c r="G13">
-        <v>2.1</v>
-      </c>
-      <c r="H13">
-        <v>11</v>
-      </c>
-      <c r="I13">
-        <v>11</v>
-      </c>
-      <c r="J13">
-        <v>1015128</v>
-      </c>
-      <c r="K13">
-        <v>2.07</v>
-      </c>
-      <c r="L13">
-        <v>14</v>
-      </c>
-      <c r="M13">
-        <v>14</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Oviedo</t>
-        </is>
-      </c>
-      <c r="P13">
-        <v>223576</v>
-      </c>
-      <c r="Q13">
-        <v>22.02</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Oviedo</t>
-        </is>
-      </c>
-      <c r="S13">
-        <v>223576</v>
-      </c>
-      <c r="T13">
-        <v>22.02</v>
-      </c>
-      <c r="U13">
-        <v>4</v>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Asturias</t>
-        </is>
-      </c>
-      <c r="X13">
-        <v>10604.0</v>
-      </c>
-      <c r="Y13">
-        <v>2.1</v>
-      </c>
-      <c r="Z13">
-        <v>100.0</v>
-      </c>
-      <c r="AA13">
-        <v>21</v>
-      </c>
-      <c r="AB13">
-        <v>1</v>
-      </c>
-      <c r="AC13">
-        <v>1015128</v>
-      </c>
-      <c r="AD13">
-        <v>2.07</v>
-      </c>
-      <c r="AE13">
-        <v>100.0</v>
-      </c>
-      <c r="AF13">
-        <v>14</v>
-      </c>
-      <c r="AG13">
-        <v>1</v>
-      </c>
-      <c r="AH13">
-        <v>78</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Oviedo</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>223576</v>
-      </c>
-      <c r="AK13">
-        <v>22.02</v>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Gijón</t>
-        </is>
-      </c>
-      <c r="AM13">
-        <v>271259</v>
-      </c>
-      <c r="AN13">
-        <v>26.72</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Baleares</t>
-        </is>
-      </c>
-      <c r="F14">
-        <v>4992.0</v>
-      </c>
-      <c r="G14">
-        <v>0.99</v>
-      </c>
-      <c r="H14">
-        <v>15</v>
-      </c>
-      <c r="I14">
-        <v>15</v>
-      </c>
-      <c r="J14">
-        <v>1249844</v>
-      </c>
-      <c r="K14">
-        <v>2.54</v>
-      </c>
-      <c r="L14">
-        <v>12</v>
-      </c>
-      <c r="M14">
-        <v>12</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Palma</t>
-        </is>
-      </c>
-      <c r="P14">
-        <v>443196</v>
-      </c>
-      <c r="Q14">
-        <v>35.46</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Palma</t>
-        </is>
-      </c>
-      <c r="S14">
-        <v>443196</v>
-      </c>
-      <c r="T14">
-        <v>35.46</v>
-      </c>
-      <c r="U14">
-        <v>4</v>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Baleares</t>
-        </is>
-      </c>
-      <c r="X14">
-        <v>4992.0</v>
-      </c>
-      <c r="Y14">
-        <v>0.99</v>
-      </c>
-      <c r="Z14">
-        <v>100.0</v>
-      </c>
       <c r="AA14">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>1</v>
       </c>
       <c r="AC14">
-        <v>1249844</v>
+        <v>998443</v>
       </c>
       <c r="AD14">
-        <v>2.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE14">
-        <v>100.0</v>
+        <v>73.17</v>
       </c>
       <c r="AF14">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AG14">
         <v>1</v>
       </c>
       <c r="AH14">
-        <v>67</v>
+        <v>293</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Palma</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="AJ14">
-        <v>443196</v>
+        <v>699007</v>
       </c>
       <c r="AK14">
-        <v>35.46</v>
+        <v>70.01</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Palma</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="AM14">
-        <v>443196</v>
+        <v>699007</v>
       </c>
       <c r="AN14">
-        <v>35.46</v>
+        <v>70.01</v>
+      </c>
+      <c r="AO14">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1461,61 +1435,61 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Canarias</t>
+          <t>Asturias</t>
         </is>
       </c>
       <c r="F15">
-        <v>7447.0</v>
+        <v>10604.0</v>
       </c>
       <c r="G15">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="H15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15">
-        <v>2258866</v>
+        <v>1015128</v>
       </c>
       <c r="K15">
-        <v>4.6</v>
+        <v>1.55</v>
       </c>
       <c r="L15">
+        <v>17</v>
+      </c>
+      <c r="M15">
+        <v>17</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Oviedo</t>
+        </is>
+      </c>
+      <c r="P15">
+        <v>223576</v>
+      </c>
+      <c r="Q15">
+        <v>22.02</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Oviedo</t>
+        </is>
+      </c>
+      <c r="S15">
+        <v>223576</v>
+      </c>
+      <c r="T15">
+        <v>22.02</v>
+      </c>
+      <c r="U15">
         <v>8</v>
       </c>
-      <c r="M15">
-        <v>8</v>
-      </c>
-      <c r="N15">
-        <v>2</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Santa Cruz de Tenerife</t>
-        </is>
-      </c>
-      <c r="P15">
-        <v>211498</v>
-      </c>
-      <c r="Q15">
-        <v>9.36</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Santa Cruz de Tenerife</t>
-        </is>
-      </c>
-      <c r="S15">
-        <v>211498</v>
-      </c>
-      <c r="T15">
-        <v>9.36</v>
-      </c>
-      <c r="U15">
-        <v>7</v>
-      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>Provincia</t>
@@ -1523,66 +1497,131 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="X15">
-        <v>4066.0</v>
+        <v>10604.0</v>
       </c>
       <c r="Y15">
-        <v>0.8</v>
+        <v>1.15</v>
       </c>
       <c r="Z15">
-        <v>54.6</v>
+        <v>100.0</v>
       </c>
       <c r="AA15">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AB15">
         <v>1</v>
       </c>
       <c r="AC15">
-        <v>1171547</v>
+        <v>1015128</v>
       </c>
       <c r="AD15">
-        <v>2.38</v>
+        <v>1.55</v>
       </c>
       <c r="AE15">
-        <v>51.86</v>
+        <v>100.0</v>
       </c>
       <c r="AF15">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AG15">
         <v>1</v>
       </c>
       <c r="AH15">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Las Palmas de Gran Canaria</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="AJ15">
-        <v>384023</v>
+        <v>223576</v>
       </c>
       <c r="AK15">
-        <v>32.78</v>
+        <v>22.02</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Las Palmas de Gran Canaria</t>
+          <t>Gijón</t>
         </is>
       </c>
       <c r="AM15">
-        <v>384023</v>
+        <v>271259</v>
       </c>
       <c r="AN15">
-        <v>32.78</v>
+        <v>26.72</v>
+      </c>
+      <c r="AO15">
+        <v>8</v>
       </c>
     </row>
     <row r="16">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Baleares</t>
+        </is>
+      </c>
+      <c r="F16">
+        <v>4992.0</v>
+      </c>
+      <c r="G16">
+        <v>0.54</v>
+      </c>
+      <c r="H16">
+        <v>19</v>
+      </c>
+      <c r="I16">
+        <v>19</v>
+      </c>
+      <c r="J16">
+        <v>1249844</v>
+      </c>
+      <c r="K16">
+        <v>1.91</v>
+      </c>
+      <c r="L16">
+        <v>14</v>
+      </c>
+      <c r="M16">
+        <v>14</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Palma</t>
+        </is>
+      </c>
+      <c r="P16">
+        <v>443196</v>
+      </c>
+      <c r="Q16">
+        <v>35.46</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Palma</t>
+        </is>
+      </c>
+      <c r="S16">
+        <v>443196</v>
+      </c>
+      <c r="T16">
+        <v>35.46</v>
+      </c>
+      <c r="U16">
+        <v>9</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>Provincia</t>
@@ -1590,63 +1629,66 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Santa Cruz de Tenerife</t>
+          <t>Baleares</t>
         </is>
       </c>
       <c r="X16">
-        <v>3381.0</v>
+        <v>4992.0</v>
       </c>
       <c r="Y16">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="Z16">
-        <v>45.4</v>
+        <v>100.0</v>
       </c>
       <c r="AA16">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="AB16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC16">
-        <v>1087319</v>
+        <v>1249844</v>
       </c>
       <c r="AD16">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="AE16">
-        <v>48.14</v>
+        <v>100.0</v>
       </c>
       <c r="AF16">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH16">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Santa Cruz de Tenerife</t>
+          <t>Palma</t>
         </is>
       </c>
       <c r="AJ16">
-        <v>211498</v>
+        <v>443196</v>
       </c>
       <c r="AK16">
-        <v>19.45</v>
+        <v>35.46</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Santa Cruz de Tenerife</t>
+          <t>Palma</t>
         </is>
       </c>
       <c r="AM16">
-        <v>211498</v>
+        <v>443196</v>
       </c>
       <c r="AN16">
-        <v>19.45</v>
+        <v>35.46</v>
+      </c>
+      <c r="AO16">
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -1657,192 +1699,260 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="F17">
-        <v>32113.0</v>
+        <v>7447.0</v>
       </c>
       <c r="G17">
-        <v>6.35</v>
+        <v>0.81</v>
       </c>
       <c r="H17">
+        <v>17</v>
+      </c>
+      <c r="I17">
+        <v>17</v>
+      </c>
+      <c r="J17">
+        <v>2258866</v>
+      </c>
+      <c r="K17">
+        <v>3.45</v>
+      </c>
+      <c r="L17">
+        <v>10</v>
+      </c>
+      <c r="M17">
+        <v>10</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Santa Cruz de Tenerife</t>
+        </is>
+      </c>
+      <c r="P17">
+        <v>211498</v>
+      </c>
+      <c r="Q17">
+        <v>9.36</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Santa Cruz de Tenerife</t>
+        </is>
+      </c>
+      <c r="S17">
+        <v>211498</v>
+      </c>
+      <c r="T17">
+        <v>9.36</v>
+      </c>
+      <c r="U17">
+        <v>17</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Canarias</t>
+        </is>
+      </c>
+      <c r="X17">
+        <v>7447.0</v>
+      </c>
+      <c r="Y17">
+        <v>0.81</v>
+      </c>
+      <c r="Z17">
+        <v>100.0</v>
+      </c>
+      <c r="AA17">
+        <v>44</v>
+      </c>
+      <c r="AB17">
+        <v>1</v>
+      </c>
+      <c r="AC17">
+        <v>2258866</v>
+      </c>
+      <c r="AD17">
+        <v>3.45</v>
+      </c>
+      <c r="AE17">
+        <v>100.0</v>
+      </c>
+      <c r="AF17">
         <v>7</v>
-      </c>
-      <c r="I17">
-        <v>7</v>
-      </c>
-      <c r="J17">
-        <v>8124126</v>
-      </c>
-      <c r="K17">
-        <v>16.54</v>
-      </c>
-      <c r="L17">
-        <v>2</v>
-      </c>
-      <c r="M17">
-        <v>2</v>
-      </c>
-      <c r="N17">
-        <v>4</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="P17">
-        <v>1713247</v>
-      </c>
-      <c r="Q17">
-        <v>21.09</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="S17">
-        <v>1713247</v>
-      </c>
-      <c r="T17">
-        <v>21.09</v>
-      </c>
-      <c r="U17">
-        <v>23</v>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="X17">
-        <v>7728.0</v>
-      </c>
-      <c r="Y17">
-        <v>1.53</v>
-      </c>
-      <c r="Z17">
-        <v>24.07</v>
-      </c>
-      <c r="AA17">
-        <v>33</v>
-      </c>
-      <c r="AB17">
-        <v>2</v>
-      </c>
-      <c r="AC17">
-        <v>5959941</v>
-      </c>
-      <c r="AD17">
-        <v>12.13</v>
-      </c>
-      <c r="AE17">
-        <v>73.36</v>
-      </c>
-      <c r="AF17">
-        <v>2</v>
       </c>
       <c r="AG17">
         <v>1</v>
       </c>
       <c r="AH17">
+        <v>88</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Santa Cruz de Tenerife</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>211498</v>
+      </c>
+      <c r="AK17">
+        <v>9.36</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Las Palmas de Gran Canaria</t>
+        </is>
+      </c>
+      <c r="AM17">
+        <v>384023</v>
+      </c>
+      <c r="AN17">
+        <v>17.0</v>
+      </c>
+      <c r="AO17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>32113.0</v>
+      </c>
+      <c r="G18">
+        <v>3.49</v>
+      </c>
+      <c r="H18">
+        <v>9</v>
+      </c>
+      <c r="I18">
+        <v>9</v>
+      </c>
+      <c r="J18">
+        <v>8124126</v>
+      </c>
+      <c r="K18">
+        <v>12.41</v>
+      </c>
+      <c r="L18">
+        <v>3</v>
+      </c>
+      <c r="M18">
+        <v>3</v>
+      </c>
+      <c r="N18">
+        <v>4</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="P18">
+        <v>1713247</v>
+      </c>
+      <c r="Q18">
+        <v>21.09</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="S18">
+        <v>1713247</v>
+      </c>
+      <c r="T18">
+        <v>21.09</v>
+      </c>
+      <c r="U18">
+        <v>62</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="X18">
+        <v>7728.0</v>
+      </c>
+      <c r="Y18">
+        <v>0.84</v>
+      </c>
+      <c r="Z18">
+        <v>24.07</v>
+      </c>
+      <c r="AA18">
+        <v>41</v>
+      </c>
+      <c r="AB18">
+        <v>2</v>
+      </c>
+      <c r="AC18">
+        <v>5959941</v>
+      </c>
+      <c r="AD18">
+        <v>9.11</v>
+      </c>
+      <c r="AE18">
+        <v>73.36</v>
+      </c>
+      <c r="AF18">
+        <v>2</v>
+      </c>
+      <c r="AG18">
+        <v>1</v>
+      </c>
+      <c r="AH18">
         <v>311</v>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="AJ17">
+      <c r="AJ18">
         <v>1713247</v>
       </c>
-      <c r="AK17">
+      <c r="AK18">
         <v>28.75</v>
       </c>
-      <c r="AL17" t="inlineStr">
+      <c r="AL18" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="AM17">
+      <c r="AM18">
         <v>1713247</v>
       </c>
-      <c r="AN17">
+      <c r="AN18">
         <v>28.75</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="X18">
-        <v>5910.0</v>
-      </c>
-      <c r="Y18">
-        <v>1.17</v>
-      </c>
-      <c r="Z18">
-        <v>18.4</v>
-      </c>
-      <c r="AA18">
-        <v>40</v>
-      </c>
-      <c r="AB18">
-        <v>4</v>
-      </c>
-      <c r="AC18">
-        <v>830429</v>
-      </c>
-      <c r="AD18">
-        <v>1.69</v>
-      </c>
-      <c r="AE18">
-        <v>10.22</v>
-      </c>
-      <c r="AF18">
-        <v>19</v>
-      </c>
-      <c r="AG18">
-        <v>3</v>
-      </c>
-      <c r="AH18">
-        <v>221</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>108352</v>
-      </c>
-      <c r="AK18">
-        <v>13.05</v>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="AM18">
-        <v>108352</v>
-      </c>
-      <c r="AN18">
-        <v>13.05</v>
+      <c r="AO18">
+        <v>47</v>
       </c>
     </row>
     <row r="19">
@@ -1853,63 +1963,66 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Gerona</t>
         </is>
       </c>
       <c r="X19">
-        <v>12172.0</v>
+        <v>5910.0</v>
       </c>
       <c r="Y19">
-        <v>2.41</v>
+        <v>0.64</v>
       </c>
       <c r="Z19">
-        <v>37.9</v>
+        <v>18.4</v>
       </c>
       <c r="AA19">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="AB19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC19">
-        <v>458226</v>
+        <v>830429</v>
       </c>
       <c r="AD19">
-        <v>0.93</v>
+        <v>1.27</v>
       </c>
       <c r="AE19">
-        <v>5.64</v>
+        <v>10.22</v>
       </c>
       <c r="AF19">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AG19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH19">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="AJ19">
-        <v>147369</v>
+        <v>108352</v>
       </c>
       <c r="AK19">
-        <v>32.16</v>
+        <v>13.05</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="AM19">
-        <v>147369</v>
+        <v>108352</v>
       </c>
       <c r="AN19">
-        <v>32.16</v>
+        <v>13.05</v>
+      </c>
+      <c r="AO19">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1920,259 +2033,268 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>Lérida</t>
+        </is>
+      </c>
+      <c r="X20">
+        <v>12172.0</v>
+      </c>
+      <c r="Y20">
+        <v>1.32</v>
+      </c>
+      <c r="Z20">
+        <v>37.9</v>
+      </c>
+      <c r="AA20">
+        <v>23</v>
+      </c>
+      <c r="AB20">
+        <v>1</v>
+      </c>
+      <c r="AC20">
+        <v>458226</v>
+      </c>
+      <c r="AD20">
+        <v>0.7</v>
+      </c>
+      <c r="AE20">
+        <v>5.64</v>
+      </c>
+      <c r="AF20">
+        <v>40</v>
+      </c>
+      <c r="AG20">
+        <v>4</v>
+      </c>
+      <c r="AH20">
+        <v>231</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Lleida</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>147369</v>
+      </c>
+      <c r="AK20">
+        <v>32.16</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Lleida</t>
+        </is>
+      </c>
+      <c r="AM20">
+        <v>147369</v>
+      </c>
+      <c r="AN20">
+        <v>32.16</v>
+      </c>
+      <c r="AO20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>Tarragona</t>
         </is>
       </c>
-      <c r="X20">
+      <c r="X21">
         <v>6303.0</v>
       </c>
-      <c r="Y20">
-        <v>1.25</v>
-      </c>
-      <c r="Z20">
+      <c r="Y21">
+        <v>0.68</v>
+      </c>
+      <c r="Z21">
         <v>19.63</v>
       </c>
-      <c r="AA20">
+      <c r="AA21">
+        <v>49</v>
+      </c>
+      <c r="AB21">
+        <v>3</v>
+      </c>
+      <c r="AC21">
+        <v>875530</v>
+      </c>
+      <c r="AD21">
+        <v>1.34</v>
+      </c>
+      <c r="AE21">
+        <v>10.78</v>
+      </c>
+      <c r="AF21">
+        <v>23</v>
+      </c>
+      <c r="AG21">
+        <v>2</v>
+      </c>
+      <c r="AH21">
+        <v>184</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Tarragona</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>143260</v>
+      </c>
+      <c r="AK21">
+        <v>16.36</v>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Tarragona</t>
+        </is>
+      </c>
+      <c r="AM21">
+        <v>143260</v>
+      </c>
+      <c r="AN21">
+        <v>16.36</v>
+      </c>
+      <c r="AO21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Castilla la Nueva</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>72564.0</v>
+      </c>
+      <c r="G22">
+        <v>7.88</v>
+      </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22">
+        <v>4</v>
+      </c>
+      <c r="J22">
+        <v>8849513</v>
+      </c>
+      <c r="K22">
+        <v>13.52</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="P22">
+        <v>3477497</v>
+      </c>
+      <c r="Q22">
+        <v>39.3</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="S22">
+        <v>3477497</v>
+      </c>
+      <c r="T22">
+        <v>39.3</v>
+      </c>
+      <c r="U22">
+        <v>68</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ciudad Real</t>
+        </is>
+      </c>
+      <c r="X22">
+        <v>19813.0</v>
+      </c>
+      <c r="Y22">
+        <v>2.15</v>
+      </c>
+      <c r="Z22">
+        <v>27.3</v>
+      </c>
+      <c r="AA22">
+        <v>8</v>
+      </c>
+      <c r="AB22">
+        <v>1</v>
+      </c>
+      <c r="AC22">
+        <v>494848</v>
+      </c>
+      <c r="AD22">
+        <v>0.76</v>
+      </c>
+      <c r="AE22">
+        <v>5.59</v>
+      </c>
+      <c r="AF22">
         <v>39</v>
       </c>
-      <c r="AB20">
+      <c r="AG22">
         <v>3</v>
       </c>
-      <c r="AC20">
-        <v>875530</v>
-      </c>
-      <c r="AD20">
-        <v>1.78</v>
-      </c>
-      <c r="AE20">
-        <v>10.78</v>
-      </c>
-      <c r="AF20">
-        <v>18</v>
-      </c>
-      <c r="AG20">
-        <v>2</v>
-      </c>
-      <c r="AH20">
-        <v>184</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Tarragona</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>143260</v>
-      </c>
-      <c r="AK20">
-        <v>16.36</v>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Tarragona</t>
-        </is>
-      </c>
-      <c r="AM20">
-        <v>143260</v>
-      </c>
-      <c r="AN20">
-        <v>16.36</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Castilla la Nueva</t>
-        </is>
-      </c>
-      <c r="F21">
-        <v>72564.0</v>
-      </c>
-      <c r="G21">
-        <v>14.34</v>
-      </c>
-      <c r="H21">
-        <v>2</v>
-      </c>
-      <c r="I21">
-        <v>2</v>
-      </c>
-      <c r="J21">
-        <v>8849513</v>
-      </c>
-      <c r="K21">
-        <v>18.01</v>
-      </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21">
-        <v>5</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="P21">
-        <v>3477497</v>
-      </c>
-      <c r="Q21">
-        <v>39.3</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="S21">
-        <v>3477497</v>
-      </c>
-      <c r="T21">
-        <v>39.3</v>
-      </c>
-      <c r="U21">
-        <v>25</v>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
+      <c r="AH22">
+        <v>102</v>
+      </c>
+      <c r="AI22" t="inlineStr">
         <is>
           <t>Ciudad Real</t>
         </is>
       </c>
-      <c r="X21">
-        <v>19813.0</v>
-      </c>
-      <c r="Y21">
-        <v>3.92</v>
-      </c>
-      <c r="Z21">
-        <v>27.3</v>
-      </c>
-      <c r="AA21">
+      <c r="AJ22">
+        <v>76087</v>
+      </c>
+      <c r="AK22">
+        <v>15.38</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Ciudad Real</t>
+        </is>
+      </c>
+      <c r="AM22">
+        <v>76087</v>
+      </c>
+      <c r="AN22">
+        <v>15.38</v>
+      </c>
+      <c r="AO22">
         <v>3</v>
-      </c>
-      <c r="AB21">
-        <v>1</v>
-      </c>
-      <c r="AC21">
-        <v>494848</v>
-      </c>
-      <c r="AD21">
-        <v>1.01</v>
-      </c>
-      <c r="AE21">
-        <v>5.59</v>
-      </c>
-      <c r="AF21">
-        <v>31</v>
-      </c>
-      <c r="AG21">
-        <v>3</v>
-      </c>
-      <c r="AH21">
-        <v>102</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Ciudad Real</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>76087</v>
-      </c>
-      <c r="AK21">
-        <v>15.38</v>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Ciudad Real</t>
-        </is>
-      </c>
-      <c r="AM21">
-        <v>76087</v>
-      </c>
-      <c r="AN21">
-        <v>15.38</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Cuenca</t>
-        </is>
-      </c>
-      <c r="X22">
-        <v>17141.0</v>
-      </c>
-      <c r="Y22">
-        <v>3.39</v>
-      </c>
-      <c r="Z22">
-        <v>23.62</v>
-      </c>
-      <c r="AA22">
-        <v>5</v>
-      </c>
-      <c r="AB22">
-        <v>2</v>
-      </c>
-      <c r="AC22">
-        <v>199859</v>
-      </c>
-      <c r="AD22">
-        <v>0.41</v>
-      </c>
-      <c r="AE22">
-        <v>2.26</v>
-      </c>
-      <c r="AF22">
-        <v>44</v>
-      </c>
-      <c r="AG22">
-        <v>5</v>
-      </c>
-      <c r="AH22">
-        <v>238</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Cuenca</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>53761</v>
-      </c>
-      <c r="AK22">
-        <v>26.9</v>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Cuenca</t>
-        </is>
-      </c>
-      <c r="AM22">
-        <v>53761</v>
-      </c>
-      <c r="AN22">
-        <v>26.9</v>
       </c>
     </row>
     <row r="23">
@@ -2183,63 +2305,66 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Cuenca</t>
         </is>
       </c>
       <c r="X23">
-        <v>12212.0</v>
+        <v>17141.0</v>
       </c>
       <c r="Y23">
-        <v>2.41</v>
+        <v>1.86</v>
       </c>
       <c r="Z23">
-        <v>16.83</v>
+        <v>23.62</v>
       </c>
       <c r="AA23">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AB23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC23">
-        <v>285839</v>
+        <v>199859</v>
       </c>
       <c r="AD23">
-        <v>0.58</v>
+        <v>0.31</v>
       </c>
       <c r="AE23">
-        <v>3.23</v>
+        <v>2.26</v>
       </c>
       <c r="AF23">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="AG23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH23">
-        <v>288</v>
+        <v>238</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Cuenca</t>
         </is>
       </c>
       <c r="AJ23">
-        <v>92798</v>
+        <v>53761</v>
       </c>
       <c r="AK23">
-        <v>32.47</v>
+        <v>26.9</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Cuenca</t>
         </is>
       </c>
       <c r="AM23">
-        <v>92798</v>
+        <v>53761</v>
       </c>
       <c r="AN23">
-        <v>32.47</v>
+        <v>26.9</v>
+      </c>
+      <c r="AO23">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2250,63 +2375,66 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="X24">
-        <v>8028.0</v>
+        <v>12212.0</v>
       </c>
       <c r="Y24">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="Z24">
-        <v>11.06</v>
+        <v>16.83</v>
       </c>
       <c r="AA24">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC24">
-        <v>7113886</v>
+        <v>285839</v>
       </c>
       <c r="AD24">
-        <v>14.48</v>
+        <v>0.44</v>
       </c>
       <c r="AE24">
-        <v>80.39</v>
+        <v>3.23</v>
       </c>
       <c r="AF24">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="AG24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH24">
-        <v>179</v>
+        <v>288</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="AJ24">
-        <v>3477497</v>
+        <v>92798</v>
       </c>
       <c r="AK24">
-        <v>48.88</v>
+        <v>32.47</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="AM24">
-        <v>3477497</v>
+        <v>92798</v>
       </c>
       <c r="AN24">
-        <v>48.88</v>
+        <v>32.47</v>
+      </c>
+      <c r="AO24">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2317,259 +2445,268 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="X25">
+        <v>8028.0</v>
+      </c>
+      <c r="Y25">
+        <v>0.87</v>
+      </c>
+      <c r="Z25">
+        <v>11.06</v>
+      </c>
+      <c r="AA25">
+        <v>38</v>
+      </c>
+      <c r="AB25">
+        <v>5</v>
+      </c>
+      <c r="AC25">
+        <v>7113886</v>
+      </c>
+      <c r="AD25">
+        <v>10.87</v>
+      </c>
+      <c r="AE25">
+        <v>80.39</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+      <c r="AG25">
+        <v>1</v>
+      </c>
+      <c r="AH25">
+        <v>179</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>3477497</v>
+      </c>
+      <c r="AK25">
+        <v>48.88</v>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="AM25">
+        <v>3477497</v>
+      </c>
+      <c r="AN25">
+        <v>48.88</v>
+      </c>
+      <c r="AO25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
           <t>Toledo</t>
         </is>
       </c>
-      <c r="X25">
+      <c r="X26">
         <v>15370.0</v>
       </c>
-      <c r="Y25">
-        <v>3.04</v>
-      </c>
-      <c r="Z25">
+      <c r="Y26">
+        <v>1.67</v>
+      </c>
+      <c r="Z26">
         <v>21.18</v>
       </c>
-      <c r="AA25">
+      <c r="AA26">
+        <v>13</v>
+      </c>
+      <c r="AB26">
+        <v>3</v>
+      </c>
+      <c r="AC26">
+        <v>755081</v>
+      </c>
+      <c r="AD26">
+        <v>1.15</v>
+      </c>
+      <c r="AE26">
+        <v>8.53</v>
+      </c>
+      <c r="AF26">
+        <v>28</v>
+      </c>
+      <c r="AG26">
+        <v>2</v>
+      </c>
+      <c r="AH26">
+        <v>204</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>87074</v>
+      </c>
+      <c r="AK26">
+        <v>11.53</v>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="AM26">
+        <v>87074</v>
+      </c>
+      <c r="AN26">
+        <v>11.53</v>
+      </c>
+      <c r="AO26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Castilla la Vieja</t>
+        </is>
+      </c>
+      <c r="F27">
+        <v>104591.0</v>
+      </c>
+      <c r="G27">
+        <v>11.36</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>3321647</v>
+      </c>
+      <c r="K27">
+        <v>5.08</v>
+      </c>
+      <c r="L27">
+        <v>7</v>
+      </c>
+      <c r="M27">
+        <v>7</v>
+      </c>
+      <c r="N27">
+        <v>11</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="P27">
+        <v>301798</v>
+      </c>
+      <c r="Q27">
+        <v>9.09</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="S27">
+        <v>301798</v>
+      </c>
+      <c r="T27">
+        <v>9.09</v>
+      </c>
+      <c r="U27">
+        <v>27</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ávila</t>
+        </is>
+      </c>
+      <c r="X27">
+        <v>8050.0</v>
+      </c>
+      <c r="Y27">
+        <v>0.87</v>
+      </c>
+      <c r="Z27">
+        <v>7.7</v>
+      </c>
+      <c r="AA27">
+        <v>37</v>
+      </c>
+      <c r="AB27">
         <v>8</v>
       </c>
-      <c r="AB25">
-        <v>3</v>
-      </c>
-      <c r="AC25">
-        <v>755081</v>
-      </c>
-      <c r="AD25">
-        <v>1.54</v>
-      </c>
-      <c r="AE25">
-        <v>8.53</v>
-      </c>
-      <c r="AF25">
-        <v>22</v>
-      </c>
-      <c r="AG25">
+      <c r="AC27">
+        <v>160738</v>
+      </c>
+      <c r="AD27">
+        <v>0.25</v>
+      </c>
+      <c r="AE27">
+        <v>4.84</v>
+      </c>
+      <c r="AF27">
+        <v>55</v>
+      </c>
+      <c r="AG27">
+        <v>8</v>
+      </c>
+      <c r="AH27">
+        <v>248</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Ávila</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>59480</v>
+      </c>
+      <c r="AK27">
+        <v>37.0</v>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Ávila</t>
+        </is>
+      </c>
+      <c r="AM27">
+        <v>59480</v>
+      </c>
+      <c r="AN27">
+        <v>37.0</v>
+      </c>
+      <c r="AO27">
         <v>2</v>
-      </c>
-      <c r="AH25">
-        <v>204</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>87074</v>
-      </c>
-      <c r="AK25">
-        <v>11.53</v>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="AM25">
-        <v>87074</v>
-      </c>
-      <c r="AN25">
-        <v>11.53</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Castilla la Vieja</t>
-        </is>
-      </c>
-      <c r="F26">
-        <v>104591.0</v>
-      </c>
-      <c r="G26">
-        <v>20.67</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>3321647</v>
-      </c>
-      <c r="K26">
-        <v>6.76</v>
-      </c>
-      <c r="L26">
-        <v>6</v>
-      </c>
-      <c r="M26">
-        <v>6</v>
-      </c>
-      <c r="N26">
-        <v>11</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="P26">
-        <v>301798</v>
-      </c>
-      <c r="Q26">
-        <v>9.09</v>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="S26">
-        <v>301798</v>
-      </c>
-      <c r="T26">
-        <v>9.09</v>
-      </c>
-      <c r="U26">
-        <v>10</v>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Ávila</t>
-        </is>
-      </c>
-      <c r="X26">
-        <v>8050.0</v>
-      </c>
-      <c r="Y26">
-        <v>1.59</v>
-      </c>
-      <c r="Z26">
-        <v>7.7</v>
-      </c>
-      <c r="AA26">
-        <v>30</v>
-      </c>
-      <c r="AB26">
-        <v>8</v>
-      </c>
-      <c r="AC26">
-        <v>160738</v>
-      </c>
-      <c r="AD26">
-        <v>0.33</v>
-      </c>
-      <c r="AE26">
-        <v>4.84</v>
-      </c>
-      <c r="AF26">
-        <v>46</v>
-      </c>
-      <c r="AG26">
-        <v>8</v>
-      </c>
-      <c r="AH26">
-        <v>248</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Ávila</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>59480</v>
-      </c>
-      <c r="AK26">
-        <v>37.0</v>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Ávila</t>
-        </is>
-      </c>
-      <c r="AM26">
-        <v>59480</v>
-      </c>
-      <c r="AN26">
-        <v>37.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Burgos</t>
-        </is>
-      </c>
-      <c r="X27">
-        <v>14291.0</v>
-      </c>
-      <c r="Y27">
-        <v>2.82</v>
-      </c>
-      <c r="Z27">
-        <v>13.66</v>
-      </c>
-      <c r="AA27">
-        <v>11</v>
-      </c>
-      <c r="AB27">
-        <v>2</v>
-      </c>
-      <c r="AC27">
-        <v>362663</v>
-      </c>
-      <c r="AD27">
-        <v>0.74</v>
-      </c>
-      <c r="AE27">
-        <v>10.92</v>
-      </c>
-      <c r="AF27">
-        <v>36</v>
-      </c>
-      <c r="AG27">
-        <v>4</v>
-      </c>
-      <c r="AH27">
-        <v>371</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Burgos</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>178370</v>
-      </c>
-      <c r="AK27">
-        <v>49.18</v>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Burgos</t>
-        </is>
-      </c>
-      <c r="AM27">
-        <v>178370</v>
-      </c>
-      <c r="AN27">
-        <v>49.18</v>
       </c>
     </row>
     <row r="28">
@@ -2580,63 +2717,66 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Cantabria</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="X28">
-        <v>5321.0</v>
+        <v>14291.0</v>
       </c>
       <c r="Y28">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="Z28">
-        <v>5.09</v>
+        <v>13.66</v>
       </c>
       <c r="AA28">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>593623</v>
+        <v>362663</v>
       </c>
       <c r="AD28">
-        <v>1.21</v>
+        <v>0.55</v>
       </c>
       <c r="AE28">
-        <v>17.87</v>
+        <v>10.92</v>
       </c>
       <c r="AF28">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AG28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH28">
-        <v>102</v>
+        <v>371</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="AJ28">
-        <v>175082</v>
+        <v>178370</v>
       </c>
       <c r="AK28">
-        <v>29.49</v>
+        <v>49.18</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="AM28">
-        <v>175082</v>
+        <v>178370</v>
       </c>
       <c r="AN28">
-        <v>29.49</v>
+        <v>49.18</v>
+      </c>
+      <c r="AO28">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2654,13 +2794,13 @@
         <v>15581.0</v>
       </c>
       <c r="Y29">
-        <v>3.08</v>
+        <v>1.69</v>
       </c>
       <c r="Z29">
         <v>14.9</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AB29">
         <v>1</v>
@@ -2669,13 +2809,13 @@
         <v>448030</v>
       </c>
       <c r="AD29">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="AE29">
         <v>13.49</v>
       </c>
       <c r="AF29">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="AG29">
         <v>3</v>
@@ -2705,6 +2845,9 @@
       <c r="AN29">
         <v>27.7</v>
       </c>
+      <c r="AO29">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="V30" t="inlineStr">
@@ -2714,63 +2857,66 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Palencia</t>
+          <t>Logroño</t>
         </is>
       </c>
       <c r="X30">
-        <v>8053.0</v>
+        <v>5045.0</v>
       </c>
       <c r="Y30">
-        <v>1.59</v>
+        <v>0.55</v>
       </c>
       <c r="Z30">
-        <v>7.7</v>
+        <v>4.82</v>
       </c>
       <c r="AA30">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AC30">
-        <v>158702</v>
+        <v>326803</v>
       </c>
       <c r="AD30">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="AE30">
-        <v>4.78</v>
+        <v>9.84</v>
       </c>
       <c r="AF30">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AG30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AH30">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Palencia</t>
+          <t>Logroño</t>
         </is>
       </c>
       <c r="AJ30">
-        <v>77369</v>
+        <v>151681</v>
       </c>
       <c r="AK30">
-        <v>48.75</v>
+        <v>46.41</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Palencia</t>
+          <t>Logroño</t>
         </is>
       </c>
       <c r="AM30">
-        <v>77369</v>
+        <v>151681</v>
       </c>
       <c r="AN30">
-        <v>48.75</v>
+        <v>46.41</v>
+      </c>
+      <c r="AO30">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2781,63 +2927,66 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Palencia</t>
         </is>
       </c>
       <c r="X31">
-        <v>5045.0</v>
+        <v>8053.0</v>
       </c>
       <c r="Y31">
-        <v>1.0</v>
+        <v>0.88</v>
       </c>
       <c r="Z31">
-        <v>4.82</v>
+        <v>7.7</v>
       </c>
       <c r="AA31">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="AB31">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AC31">
-        <v>326803</v>
+        <v>158702</v>
       </c>
       <c r="AD31">
-        <v>0.67</v>
+        <v>0.24</v>
       </c>
       <c r="AE31">
-        <v>9.84</v>
+        <v>4.78</v>
       </c>
       <c r="AF31">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="AG31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AH31">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Logroño</t>
+          <t>Palencia</t>
         </is>
       </c>
       <c r="AJ31">
-        <v>151681</v>
+        <v>77369</v>
       </c>
       <c r="AK31">
-        <v>46.41</v>
+        <v>48.75</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Logroño</t>
+          <t>Palencia</t>
         </is>
       </c>
       <c r="AM31">
-        <v>151681</v>
+        <v>77369</v>
       </c>
       <c r="AN31">
-        <v>46.41</v>
+        <v>48.75</v>
+      </c>
+      <c r="AO31">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2855,13 +3004,13 @@
         <v>12350.0</v>
       </c>
       <c r="Y32">
-        <v>2.44</v>
+        <v>1.34</v>
       </c>
       <c r="Z32">
         <v>11.81</v>
       </c>
       <c r="AA32">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AB32">
         <v>3</v>
@@ -2870,13 +3019,13 @@
         <v>328446</v>
       </c>
       <c r="AD32">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AE32">
         <v>9.89</v>
       </c>
       <c r="AF32">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="AG32">
         <v>5</v>
@@ -2906,6 +3055,9 @@
       <c r="AN32">
         <v>44.32</v>
       </c>
+      <c r="AO32">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="V33" t="inlineStr">
@@ -2915,63 +3067,66 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Segovia</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="X33">
-        <v>6923.0</v>
+        <v>5321.0</v>
       </c>
       <c r="Y33">
-        <v>1.37</v>
+        <v>0.58</v>
       </c>
       <c r="Z33">
-        <v>6.62</v>
+        <v>5.09</v>
       </c>
       <c r="AA33">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="AB33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC33">
-        <v>158251</v>
+        <v>593623</v>
       </c>
       <c r="AD33">
-        <v>0.32</v>
+        <v>0.91</v>
       </c>
       <c r="AE33">
-        <v>4.76</v>
+        <v>17.87</v>
       </c>
       <c r="AF33">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AG33">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AH33">
-        <v>209</v>
+        <v>102</v>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Segovia</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="AJ33">
-        <v>52189</v>
+        <v>175082</v>
       </c>
       <c r="AK33">
-        <v>32.98</v>
+        <v>29.49</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Segovia</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="AM33">
-        <v>52189</v>
+        <v>175082</v>
       </c>
       <c r="AN33">
-        <v>32.98</v>
+        <v>29.49</v>
+      </c>
+      <c r="AO33">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2982,63 +3137,66 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Soria</t>
+          <t>Segovia</t>
         </is>
       </c>
       <c r="X34">
-        <v>10306.0</v>
+        <v>6923.0</v>
       </c>
       <c r="Y34">
-        <v>2.04</v>
+        <v>0.75</v>
       </c>
       <c r="Z34">
-        <v>9.85</v>
+        <v>6.62</v>
       </c>
       <c r="AA34">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="AB34">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC34">
-        <v>90183</v>
+        <v>158251</v>
       </c>
       <c r="AD34">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="AE34">
-        <v>2.72</v>
+        <v>4.76</v>
       </c>
       <c r="AF34">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AG34">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH34">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Soria</t>
+          <t>Segovia</t>
         </is>
       </c>
       <c r="AJ34">
-        <v>40941</v>
+        <v>52189</v>
       </c>
       <c r="AK34">
-        <v>45.4</v>
+        <v>32.98</v>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>Soria</t>
+          <t>Segovia</t>
         </is>
       </c>
       <c r="AM34">
-        <v>40941</v>
+        <v>52189</v>
       </c>
       <c r="AN34">
-        <v>45.4</v>
+        <v>32.98</v>
+      </c>
+      <c r="AO34">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -3049,63 +3207,66 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Soria</t>
         </is>
       </c>
       <c r="X35">
-        <v>8110.0</v>
+        <v>10306.0</v>
       </c>
       <c r="Y35">
-        <v>1.6</v>
+        <v>1.12</v>
       </c>
       <c r="Z35">
-        <v>7.75</v>
+        <v>9.85</v>
       </c>
       <c r="AA35">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AB35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC35">
-        <v>528644</v>
+        <v>90183</v>
       </c>
       <c r="AD35">
-        <v>1.08</v>
+        <v>0.14</v>
       </c>
       <c r="AE35">
-        <v>15.92</v>
+        <v>2.72</v>
       </c>
       <c r="AF35">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="AG35">
+        <v>11</v>
+      </c>
+      <c r="AH35">
+        <v>183</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Soria</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>40941</v>
+      </c>
+      <c r="AK35">
+        <v>45.4</v>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Soria</t>
+        </is>
+      </c>
+      <c r="AM35">
+        <v>40941</v>
+      </c>
+      <c r="AN35">
+        <v>45.4</v>
+      </c>
+      <c r="AO35">
         <v>2</v>
-      </c>
-      <c r="AH35">
-        <v>225</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>301798</v>
-      </c>
-      <c r="AK35">
-        <v>57.09</v>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="AM35">
-        <v>301798</v>
-      </c>
-      <c r="AN35">
-        <v>57.09</v>
       </c>
     </row>
     <row r="36">
@@ -3116,195 +3277,201 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="X36">
+        <v>8110.0</v>
+      </c>
+      <c r="Y36">
+        <v>0.88</v>
+      </c>
+      <c r="Z36">
+        <v>7.75</v>
+      </c>
+      <c r="AA36">
+        <v>35</v>
+      </c>
+      <c r="AB36">
+        <v>6</v>
+      </c>
+      <c r="AC36">
+        <v>528644</v>
+      </c>
+      <c r="AD36">
+        <v>0.81</v>
+      </c>
+      <c r="AE36">
+        <v>15.92</v>
+      </c>
+      <c r="AF36">
+        <v>38</v>
+      </c>
+      <c r="AG36">
+        <v>2</v>
+      </c>
+      <c r="AH36">
+        <v>225</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>301798</v>
+      </c>
+      <c r="AK36">
+        <v>57.09</v>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="AM36">
+        <v>301798</v>
+      </c>
+      <c r="AN36">
+        <v>57.09</v>
+      </c>
+      <c r="AO36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
           <t>Zamora</t>
         </is>
       </c>
-      <c r="X36">
+      <c r="X37">
         <v>10561.0</v>
       </c>
-      <c r="Y36">
-        <v>2.09</v>
-      </c>
-      <c r="Z36">
+      <c r="Y37">
+        <v>1.15</v>
+      </c>
+      <c r="Z37">
         <v>10.1</v>
       </c>
-      <c r="AA36">
-        <v>22</v>
-      </c>
-      <c r="AB36">
+      <c r="AA37">
+        <v>28</v>
+      </c>
+      <c r="AB37">
         <v>4</v>
       </c>
-      <c r="AC36">
+      <c r="AC37">
         <v>165564</v>
       </c>
-      <c r="AD36">
-        <v>0.34</v>
-      </c>
-      <c r="AE36">
+      <c r="AD37">
+        <v>0.25</v>
+      </c>
+      <c r="AE37">
         <v>4.98</v>
       </c>
-      <c r="AF36">
-        <v>45</v>
-      </c>
-      <c r="AG36">
+      <c r="AF37">
+        <v>54</v>
+      </c>
+      <c r="AG37">
         <v>7</v>
       </c>
-      <c r="AH36">
+      <c r="AH37">
         <v>248</v>
       </c>
-      <c r="AI36" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>Zamora</t>
         </is>
       </c>
-      <c r="AJ36">
+      <c r="AJ37">
         <v>59857</v>
       </c>
-      <c r="AK36">
+      <c r="AK37">
         <v>36.15</v>
       </c>
-      <c r="AL36" t="inlineStr">
+      <c r="AL37" t="inlineStr">
         <is>
           <t>Zamora</t>
         </is>
       </c>
-      <c r="AM36">
+      <c r="AM37">
         <v>59857</v>
       </c>
-      <c r="AN36">
+      <c r="AN37">
         <v>36.15</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="D37" t="inlineStr">
+      <c r="AO37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Extremadura</t>
-        </is>
-      </c>
-      <c r="F37">
-        <v>41634.0</v>
-      </c>
-      <c r="G37">
-        <v>8.23</v>
-      </c>
-      <c r="H37">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
+      <c r="F38">
+        <v>109884.01</v>
+      </c>
+      <c r="G38">
+        <v>11.94</v>
+      </c>
+      <c r="H38">
+        <v>2</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38">
+        <v>11089511</v>
+      </c>
+      <c r="K38">
+        <v>16.95</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+      <c r="N38">
         <v>6</v>
       </c>
-      <c r="I37">
-        <v>6</v>
-      </c>
-      <c r="J37">
-        <v>1053345</v>
-      </c>
-      <c r="K37">
-        <v>2.14</v>
-      </c>
-      <c r="L37">
-        <v>13</v>
-      </c>
-      <c r="M37">
-        <v>13</v>
-      </c>
-      <c r="N37">
-        <v>2</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Badajoz</t>
-        </is>
-      </c>
-      <c r="P37">
-        <v>150870</v>
-      </c>
-      <c r="Q37">
-        <v>14.32</v>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Badajoz</t>
-        </is>
-      </c>
-      <c r="S37">
-        <v>150870</v>
-      </c>
-      <c r="T37">
-        <v>14.32</v>
-      </c>
-      <c r="U37">
-        <v>4</v>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Badajoz</t>
-        </is>
-      </c>
-      <c r="X37">
-        <v>21766.0</v>
-      </c>
-      <c r="Y37">
-        <v>4.3</v>
-      </c>
-      <c r="Z37">
-        <v>52.28</v>
-      </c>
-      <c r="AA37">
-        <v>1</v>
-      </c>
-      <c r="AB37">
-        <v>1</v>
-      </c>
-      <c r="AC37">
-        <v>665155</v>
-      </c>
-      <c r="AD37">
-        <v>1.35</v>
-      </c>
-      <c r="AE37">
-        <v>63.15</v>
-      </c>
-      <c r="AF37">
-        <v>25</v>
-      </c>
-      <c r="AG37">
-        <v>1</v>
-      </c>
-      <c r="AH37">
-        <v>165</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Badajoz</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>150870</v>
-      </c>
-      <c r="AK37">
-        <v>22.68</v>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>Badajoz</t>
-        </is>
-      </c>
-      <c r="AM37">
-        <v>150870</v>
-      </c>
-      <c r="AN37">
-        <v>22.68</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>La Habana</t>
+        </is>
+      </c>
+      <c r="P38">
+        <v>2137847</v>
+      </c>
+      <c r="Q38">
+        <v>19.28</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>La Habana</t>
+        </is>
+      </c>
+      <c r="S38">
+        <v>2137847</v>
+      </c>
+      <c r="T38">
+        <v>19.28</v>
+      </c>
+      <c r="U38">
+        <v>85</v>
+      </c>
       <c r="V38" t="inlineStr">
         <is>
           <t>Provincia</t>
@@ -3312,128 +3479,69 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Cáceres</t>
+          <t>La Habana</t>
         </is>
       </c>
       <c r="X38">
-        <v>19868.0</v>
+        <v>7804.03</v>
       </c>
       <c r="Y38">
-        <v>3.93</v>
+        <v>0.85</v>
       </c>
       <c r="Z38">
-        <v>47.72</v>
+        <v>7.1</v>
       </c>
       <c r="AA38">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AB38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC38">
-        <v>388190</v>
+        <v>2821429</v>
       </c>
       <c r="AD38">
-        <v>0.79</v>
+        <v>4.31</v>
       </c>
       <c r="AE38">
-        <v>36.85</v>
+        <v>25.44</v>
       </c>
       <c r="AF38">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="AG38">
         <v>2</v>
       </c>
       <c r="AH38">
-        <v>223</v>
+        <v>18</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Cáceres</t>
+          <t>La Habana</t>
         </is>
       </c>
       <c r="AJ38">
-        <v>96598</v>
+        <v>2137847</v>
       </c>
       <c r="AK38">
-        <v>24.88</v>
+        <v>75.77</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Cáceres</t>
+          <t>La Habana</t>
         </is>
       </c>
       <c r="AM38">
-        <v>96598</v>
+        <v>2137847</v>
       </c>
       <c r="AN38">
-        <v>24.88</v>
+        <v>75.77</v>
+      </c>
+      <c r="AO38">
+        <v>22</v>
       </c>
     </row>
     <row r="39">
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Galicia</t>
-        </is>
-      </c>
-      <c r="F39">
-        <v>29574.0</v>
-      </c>
-      <c r="G39">
-        <v>5.84</v>
-      </c>
-      <c r="H39">
-        <v>8</v>
-      </c>
-      <c r="I39">
-        <v>8</v>
-      </c>
-      <c r="J39">
-        <v>2714741</v>
-      </c>
-      <c r="K39">
-        <v>5.53</v>
-      </c>
-      <c r="L39">
-        <v>7</v>
-      </c>
-      <c r="M39">
-        <v>7</v>
-      </c>
-      <c r="N39">
-        <v>4</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Santiago de Compostela</t>
-        </is>
-      </c>
-      <c r="P39">
-        <v>100842</v>
-      </c>
-      <c r="Q39">
-        <v>3.71</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Santiago de Compostela</t>
-        </is>
-      </c>
-      <c r="S39">
-        <v>100842</v>
-      </c>
-      <c r="T39">
-        <v>3.71</v>
-      </c>
-      <c r="U39">
-        <v>9</v>
-      </c>
       <c r="V39" t="inlineStr">
         <is>
           <t>Provincia</t>
@@ -3441,63 +3549,66 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>A Coruña</t>
+          <t>Matanzas</t>
         </is>
       </c>
       <c r="X39">
-        <v>7950.0</v>
+        <v>7629.42</v>
       </c>
       <c r="Y39">
-        <v>1.57</v>
+        <v>0.83</v>
       </c>
       <c r="Z39">
-        <v>26.88</v>
+        <v>6.94</v>
       </c>
       <c r="AA39">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AB39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AC39">
-        <v>1135623</v>
+        <v>699733</v>
       </c>
       <c r="AD39">
-        <v>2.31</v>
+        <v>1.07</v>
       </c>
       <c r="AE39">
-        <v>41.83</v>
+        <v>6.31</v>
       </c>
       <c r="AF39">
+        <v>30</v>
+      </c>
+      <c r="AG39">
+        <v>6</v>
+      </c>
+      <c r="AH39">
         <v>12</v>
       </c>
-      <c r="AG39">
-        <v>1</v>
-      </c>
-      <c r="AH39">
-        <v>93</v>
-      </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>A Coruña</t>
+          <t>Matanzas</t>
         </is>
       </c>
       <c r="AJ39">
-        <v>251277</v>
+        <v>710127</v>
       </c>
       <c r="AK39">
-        <v>22.13</v>
+        <v>101.49</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>A Coruña</t>
+          <t>Matanzas</t>
         </is>
       </c>
       <c r="AM39">
-        <v>251277</v>
+        <v>163631</v>
       </c>
       <c r="AN39">
-        <v>22.13</v>
+        <v>23.38</v>
+      </c>
+      <c r="AO39">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -3508,63 +3619,66 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Lugo</t>
+          <t>Pinar del Río</t>
         </is>
       </c>
       <c r="X40">
-        <v>9856.0</v>
+        <v>11974.29</v>
       </c>
       <c r="Y40">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>33.33</v>
+        <v>10.9</v>
       </c>
       <c r="AA40">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC40">
-        <v>326022</v>
+        <v>869469</v>
       </c>
       <c r="AD40">
-        <v>0.66</v>
+        <v>1.33</v>
       </c>
       <c r="AE40">
-        <v>12.01</v>
+        <v>7.84</v>
       </c>
       <c r="AF40">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AG40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH40">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Lugo</t>
+          <t>Pinar del Río</t>
         </is>
       </c>
       <c r="AJ40">
-        <v>100071</v>
+        <v>575545</v>
       </c>
       <c r="AK40">
-        <v>30.69</v>
+        <v>66.19</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Lugo</t>
+          <t>Pinar del Río</t>
         </is>
       </c>
       <c r="AM40">
-        <v>100071</v>
+        <v>191081</v>
       </c>
       <c r="AN40">
-        <v>30.69</v>
+        <v>21.98</v>
+      </c>
+      <c r="AO40">
+        <v>6</v>
       </c>
     </row>
     <row r="41">
@@ -3575,63 +3689,66 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Ourense</t>
+          <t>Puerto Príncipe</t>
         </is>
       </c>
       <c r="X41">
-        <v>7273.0</v>
+        <v>24534.0</v>
       </c>
       <c r="Y41">
-        <v>1.44</v>
+        <v>2.67</v>
       </c>
       <c r="Z41">
-        <v>24.59</v>
+        <v>22.33</v>
       </c>
       <c r="AA41">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="AB41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC41">
-        <v>305278</v>
+        <v>1296212</v>
       </c>
       <c r="AD41">
-        <v>0.62</v>
+        <v>1.98</v>
       </c>
       <c r="AE41">
-        <v>11.25</v>
+        <v>11.69</v>
       </c>
       <c r="AF41">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="AG41">
         <v>4</v>
       </c>
       <c r="AH41">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Ourense</t>
+          <t>Camagüey</t>
         </is>
       </c>
       <c r="AJ41">
-        <v>105609</v>
+        <v>756064</v>
       </c>
       <c r="AK41">
-        <v>34.59</v>
+        <v>58.33</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>Ourense</t>
+          <t>Camagüey</t>
         </is>
       </c>
       <c r="AM41">
-        <v>105609</v>
+        <v>333251</v>
       </c>
       <c r="AN41">
-        <v>34.59</v>
+        <v>25.71</v>
+      </c>
+      <c r="AO41">
+        <v>10</v>
       </c>
     </row>
     <row r="42">
@@ -3642,195 +3759,201 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Pontevedra</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="X42">
-        <v>4495.0</v>
+        <v>22776.4</v>
       </c>
       <c r="Y42">
-        <v>0.89</v>
+        <v>2.47</v>
       </c>
       <c r="Z42">
-        <v>15.2</v>
+        <v>20.73</v>
       </c>
       <c r="AA42">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="AB42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC42">
-        <v>947818</v>
+        <v>1592772</v>
       </c>
       <c r="AD42">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="AE42">
-        <v>34.91</v>
+        <v>14.36</v>
       </c>
       <c r="AF42">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AG42">
+        <v>3</v>
+      </c>
+      <c r="AH42">
+        <v>29</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>245959</v>
+      </c>
+      <c r="AK42">
+        <v>15.44</v>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="AM42">
+        <v>245959</v>
+      </c>
+      <c r="AN42">
+        <v>15.44</v>
+      </c>
+      <c r="AO42">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Santiago de Cuba</t>
+        </is>
+      </c>
+      <c r="X43">
+        <v>35165.87</v>
+      </c>
+      <c r="Y43">
+        <v>3.82</v>
+      </c>
+      <c r="Z43">
+        <v>32.0</v>
+      </c>
+      <c r="AA43">
         <v>2</v>
-      </c>
-      <c r="AH42">
-        <v>61</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Pontevedra</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>83339</v>
-      </c>
-      <c r="AK42">
-        <v>8.79</v>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>Vigo</t>
-        </is>
-      </c>
-      <c r="AM42">
-        <v>295735</v>
-      </c>
-      <c r="AN42">
-        <v>31.2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Murcia</t>
-        </is>
-      </c>
-      <c r="F43">
-        <v>26239.0</v>
-      </c>
-      <c r="G43">
-        <v>5.19</v>
-      </c>
-      <c r="H43">
-        <v>9</v>
-      </c>
-      <c r="I43">
-        <v>9</v>
-      </c>
-      <c r="J43">
-        <v>1977740</v>
-      </c>
-      <c r="K43">
-        <v>4.03</v>
-      </c>
-      <c r="L43">
-        <v>10</v>
-      </c>
-      <c r="M43">
-        <v>10</v>
-      </c>
-      <c r="N43">
-        <v>2</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Murcia</t>
-        </is>
-      </c>
-      <c r="P43">
-        <v>477631</v>
-      </c>
-      <c r="Q43">
-        <v>24.15</v>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Murcia</t>
-        </is>
-      </c>
-      <c r="S43">
-        <v>477631</v>
-      </c>
-      <c r="T43">
-        <v>24.15</v>
-      </c>
-      <c r="U43">
-        <v>6</v>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
-      </c>
-      <c r="X43">
-        <v>14926.0</v>
-      </c>
-      <c r="Y43">
-        <v>2.95</v>
-      </c>
-      <c r="Z43">
-        <v>56.88</v>
-      </c>
-      <c r="AA43">
-        <v>9</v>
       </c>
       <c r="AB43">
         <v>1</v>
       </c>
       <c r="AC43">
-        <v>390751</v>
+        <v>3809896</v>
       </c>
       <c r="AD43">
-        <v>0.8</v>
+        <v>5.82</v>
       </c>
       <c r="AE43">
-        <v>19.76</v>
+        <v>34.36</v>
       </c>
       <c r="AF43">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="AG43">
+        <v>1</v>
+      </c>
+      <c r="AH43">
+        <v>52</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Santiago de Cuba</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>1037339</v>
+      </c>
+      <c r="AK43">
+        <v>27.23</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Santiago de Cuba</t>
+        </is>
+      </c>
+      <c r="AM43">
+        <v>507167</v>
+      </c>
+      <c r="AN43">
+        <v>13.31</v>
+      </c>
+      <c r="AO43">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="F44">
+        <v>41634.0</v>
+      </c>
+      <c r="G44">
+        <v>4.52</v>
+      </c>
+      <c r="H44">
+        <v>8</v>
+      </c>
+      <c r="I44">
+        <v>8</v>
+      </c>
+      <c r="J44">
+        <v>1053345</v>
+      </c>
+      <c r="K44">
+        <v>1.61</v>
+      </c>
+      <c r="L44">
+        <v>16</v>
+      </c>
+      <c r="M44">
+        <v>16</v>
+      </c>
+      <c r="N44">
         <v>2</v>
       </c>
-      <c r="AH43">
-        <v>87</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>175068</v>
-      </c>
-      <c r="AK43">
-        <v>44.8</v>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
-      </c>
-      <c r="AM43">
-        <v>175068</v>
-      </c>
-      <c r="AN43">
-        <v>44.8</v>
-      </c>
-    </row>
-    <row r="44">
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Badajoz</t>
+        </is>
+      </c>
+      <c r="P44">
+        <v>150870</v>
+      </c>
+      <c r="Q44">
+        <v>14.32</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Badajoz</t>
+        </is>
+      </c>
+      <c r="S44">
+        <v>150870</v>
+      </c>
+      <c r="T44">
+        <v>14.32</v>
+      </c>
+      <c r="U44">
+        <v>8</v>
+      </c>
       <c r="V44" t="inlineStr">
         <is>
           <t>Provincia</t>
@@ -3838,192 +3961,136 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Murcia</t>
+          <t>Badajoz</t>
         </is>
       </c>
       <c r="X44">
-        <v>11313.0</v>
+        <v>21766.0</v>
       </c>
       <c r="Y44">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="Z44">
-        <v>43.12</v>
+        <v>52.28</v>
       </c>
       <c r="AA44">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="AB44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC44">
-        <v>1586989</v>
+        <v>665155</v>
       </c>
       <c r="AD44">
-        <v>3.23</v>
+        <v>1.02</v>
       </c>
       <c r="AE44">
-        <v>80.24</v>
+        <v>63.15</v>
       </c>
       <c r="AF44">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="AG44">
         <v>1</v>
       </c>
       <c r="AH44">
-        <v>45</v>
+        <v>165</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Murcia</t>
+          <t>Badajoz</t>
         </is>
       </c>
       <c r="AJ44">
-        <v>477631</v>
+        <v>150870</v>
       </c>
       <c r="AK44">
-        <v>30.1</v>
+        <v>22.68</v>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>Murcia</t>
+          <t>Badajoz</t>
         </is>
       </c>
       <c r="AM44">
-        <v>477631</v>
+        <v>150870</v>
       </c>
       <c r="AN44">
-        <v>30.1</v>
+        <v>22.68</v>
+      </c>
+      <c r="AO44">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Navarra</t>
-        </is>
-      </c>
-      <c r="F45">
-        <v>10390.0</v>
-      </c>
-      <c r="G45">
-        <v>2.05</v>
-      </c>
-      <c r="H45">
-        <v>12</v>
-      </c>
-      <c r="I45">
-        <v>12</v>
-      </c>
-      <c r="J45">
-        <v>683854</v>
-      </c>
-      <c r="K45">
-        <v>1.39</v>
-      </c>
-      <c r="L45">
-        <v>15</v>
-      </c>
-      <c r="M45">
-        <v>15</v>
-      </c>
-      <c r="N45">
-        <v>1</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Pamplona</t>
-        </is>
-      </c>
-      <c r="P45">
-        <v>209676</v>
-      </c>
-      <c r="Q45">
-        <v>30.66</v>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Pamplona</t>
-        </is>
-      </c>
-      <c r="S45">
-        <v>209676</v>
-      </c>
-      <c r="T45">
-        <v>30.66</v>
-      </c>
-      <c r="U45">
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="X45">
+        <v>19868.0</v>
+      </c>
+      <c r="Y45">
+        <v>2.16</v>
+      </c>
+      <c r="Z45">
+        <v>47.72</v>
+      </c>
+      <c r="AA45">
+        <v>7</v>
+      </c>
+      <c r="AB45">
+        <v>2</v>
+      </c>
+      <c r="AC45">
+        <v>388190</v>
+      </c>
+      <c r="AD45">
+        <v>0.59</v>
+      </c>
+      <c r="AE45">
+        <v>36.85</v>
+      </c>
+      <c r="AF45">
+        <v>43</v>
+      </c>
+      <c r="AG45">
+        <v>2</v>
+      </c>
+      <c r="AH45">
+        <v>223</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>96598</v>
+      </c>
+      <c r="AK45">
+        <v>24.88</v>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="AM45">
+        <v>96598</v>
+      </c>
+      <c r="AN45">
+        <v>24.88</v>
+      </c>
+      <c r="AO45">
         <v>3</v>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Navarra</t>
-        </is>
-      </c>
-      <c r="X45">
-        <v>10390.0</v>
-      </c>
-      <c r="Y45">
-        <v>2.05</v>
-      </c>
-      <c r="Z45">
-        <v>100.0</v>
-      </c>
-      <c r="AA45">
-        <v>23</v>
-      </c>
-      <c r="AB45">
-        <v>1</v>
-      </c>
-      <c r="AC45">
-        <v>683854</v>
-      </c>
-      <c r="AD45">
-        <v>1.39</v>
-      </c>
-      <c r="AE45">
-        <v>100.0</v>
-      </c>
-      <c r="AF45">
-        <v>24</v>
-      </c>
-      <c r="AG45">
-        <v>1</v>
-      </c>
-      <c r="AH45">
-        <v>272</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Pamplona</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>209676</v>
-      </c>
-      <c r="AK45">
-        <v>30.66</v>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>Pamplona</t>
-        </is>
-      </c>
-      <c r="AM45">
-        <v>209676</v>
-      </c>
-      <c r="AN45">
-        <v>30.66</v>
       </c>
     </row>
     <row r="46">
@@ -4034,14 +4101,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Galicia</t>
         </is>
       </c>
       <c r="F46">
-        <v>23255.0</v>
+        <v>29574.0</v>
       </c>
       <c r="G46">
-        <v>4.6</v>
+        <v>3.21</v>
       </c>
       <c r="H46">
         <v>10</v>
@@ -4050,44 +4117,44 @@
         <v>10</v>
       </c>
       <c r="J46">
-        <v>5425182</v>
+        <v>2714741</v>
       </c>
       <c r="K46">
-        <v>11.04</v>
+        <v>4.15</v>
       </c>
       <c r="L46">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M46">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>València</t>
+          <t>Santiago de Compostela</t>
         </is>
       </c>
       <c r="P46">
-        <v>841558</v>
+        <v>100842</v>
       </c>
       <c r="Q46">
-        <v>15.51</v>
+        <v>3.71</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>València</t>
+          <t>Santiago de Compostela</t>
         </is>
       </c>
       <c r="S46">
-        <v>841558</v>
+        <v>100842</v>
       </c>
       <c r="T46">
-        <v>15.51</v>
+        <v>3.71</v>
       </c>
       <c r="U46">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -4096,63 +4163,66 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Alicante</t>
+          <t>La Coruña</t>
         </is>
       </c>
       <c r="X46">
-        <v>5817.0</v>
+        <v>7950.0</v>
       </c>
       <c r="Y46">
-        <v>1.15</v>
+        <v>0.86</v>
       </c>
       <c r="Z46">
-        <v>25.01</v>
+        <v>26.88</v>
       </c>
       <c r="AA46">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AB46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC46">
-        <v>2033566</v>
+        <v>1135623</v>
       </c>
       <c r="AD46">
-        <v>4.14</v>
+        <v>1.74</v>
       </c>
       <c r="AE46">
-        <v>37.48</v>
+        <v>41.83</v>
       </c>
       <c r="AF46">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AG46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH46">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Alicante</t>
+          <t>A Coruña</t>
         </is>
       </c>
       <c r="AJ46">
-        <v>2033566</v>
+        <v>251277</v>
       </c>
       <c r="AK46">
-        <v>100.0</v>
+        <v>22.13</v>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Alacant</t>
+          <t>A Coruña</t>
         </is>
       </c>
       <c r="AM46">
-        <v>365586</v>
+        <v>251277</v>
       </c>
       <c r="AN46">
-        <v>17.98</v>
+        <v>22.13</v>
+      </c>
+      <c r="AO46">
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -4163,63 +4233,66 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Castellón</t>
+          <t>Lugo</t>
         </is>
       </c>
       <c r="X47">
-        <v>6632.0</v>
+        <v>9856.0</v>
       </c>
       <c r="Y47">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="Z47">
-        <v>28.52</v>
+        <v>33.33</v>
       </c>
       <c r="AA47">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC47">
-        <v>627620</v>
+        <v>326022</v>
       </c>
       <c r="AD47">
-        <v>1.28</v>
+        <v>0.5</v>
       </c>
       <c r="AE47">
-        <v>11.57</v>
+        <v>12.01</v>
       </c>
       <c r="AF47">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="AG47">
         <v>3</v>
       </c>
       <c r="AH47">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Castelló de la Plana</t>
+          <t>Lugo</t>
         </is>
       </c>
       <c r="AJ47">
-        <v>183709</v>
+        <v>100071</v>
       </c>
       <c r="AK47">
-        <v>29.27</v>
+        <v>30.69</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>Castelló de la Plana</t>
+          <t>Lugo</t>
         </is>
       </c>
       <c r="AM47">
-        <v>183709</v>
+        <v>100071</v>
       </c>
       <c r="AN47">
-        <v>29.27</v>
+        <v>30.69</v>
+      </c>
+      <c r="AO47">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -4230,195 +4303,201 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Orense</t>
         </is>
       </c>
       <c r="X48">
-        <v>10806.0</v>
+        <v>7273.0</v>
       </c>
       <c r="Y48">
-        <v>2.14</v>
+        <v>0.79</v>
       </c>
       <c r="Z48">
-        <v>46.47</v>
+        <v>24.59</v>
       </c>
       <c r="AA48">
+        <v>46</v>
+      </c>
+      <c r="AB48">
+        <v>3</v>
+      </c>
+      <c r="AC48">
+        <v>305278</v>
+      </c>
+      <c r="AD48">
+        <v>0.47</v>
+      </c>
+      <c r="AE48">
+        <v>11.25</v>
+      </c>
+      <c r="AF48">
+        <v>50</v>
+      </c>
+      <c r="AG48">
+        <v>4</v>
+      </c>
+      <c r="AH48">
+        <v>92</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Ourense</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>105609</v>
+      </c>
+      <c r="AK48">
+        <v>34.59</v>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Ourense</t>
+        </is>
+      </c>
+      <c r="AM48">
+        <v>105609</v>
+      </c>
+      <c r="AN48">
+        <v>34.59</v>
+      </c>
+      <c r="AO48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Pontevedra</t>
+        </is>
+      </c>
+      <c r="X49">
+        <v>4495.0</v>
+      </c>
+      <c r="Y49">
+        <v>0.49</v>
+      </c>
+      <c r="Z49">
+        <v>15.2</v>
+      </c>
+      <c r="AA49">
+        <v>55</v>
+      </c>
+      <c r="AB49">
+        <v>4</v>
+      </c>
+      <c r="AC49">
+        <v>947818</v>
+      </c>
+      <c r="AD49">
+        <v>1.45</v>
+      </c>
+      <c r="AE49">
+        <v>34.91</v>
+      </c>
+      <c r="AF49">
         <v>20</v>
       </c>
-      <c r="AB48">
-        <v>1</v>
-      </c>
-      <c r="AC48">
-        <v>2763996</v>
-      </c>
-      <c r="AD48">
-        <v>5.63</v>
-      </c>
-      <c r="AE48">
-        <v>50.95</v>
-      </c>
-      <c r="AF48">
-        <v>3</v>
-      </c>
-      <c r="AG48">
-        <v>1</v>
-      </c>
-      <c r="AH48">
-        <v>266</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>València</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>841558</v>
-      </c>
-      <c r="AK48">
-        <v>30.45</v>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>València</t>
-        </is>
-      </c>
-      <c r="AM48">
-        <v>841558</v>
-      </c>
-      <c r="AN48">
-        <v>30.45</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="D49" t="inlineStr">
+      <c r="AG49">
+        <v>2</v>
+      </c>
+      <c r="AH49">
+        <v>61</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Pontevedra</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>83339</v>
+      </c>
+      <c r="AK49">
+        <v>8.79</v>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Vigo</t>
+        </is>
+      </c>
+      <c r="AM49">
+        <v>295735</v>
+      </c>
+      <c r="AN49">
+        <v>31.2</v>
+      </c>
+      <c r="AO49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Regiones Vascongadas</t>
-        </is>
-      </c>
-      <c r="F49">
-        <v>7235.0</v>
-      </c>
-      <c r="G49">
-        <v>1.43</v>
-      </c>
-      <c r="H49">
-        <v>14</v>
-      </c>
-      <c r="I49">
-        <v>14</v>
-      </c>
-      <c r="J49">
-        <v>2242343</v>
-      </c>
-      <c r="K49">
-        <v>4.56</v>
-      </c>
-      <c r="L49">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Territorios en el Golfo de Guinea</t>
+        </is>
+      </c>
+      <c r="F50">
+        <v>28051.0</v>
+      </c>
+      <c r="G50">
+        <v>3.05</v>
+      </c>
+      <c r="H50">
+        <v>11</v>
+      </c>
+      <c r="I50">
+        <v>11</v>
+      </c>
+      <c r="J50">
+        <v>1225377</v>
+      </c>
+      <c r="K50">
+        <v>1.87</v>
+      </c>
+      <c r="L50">
+        <v>15</v>
+      </c>
+      <c r="M50">
+        <v>15</v>
+      </c>
+      <c r="N50">
+        <v>2</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Malabo</t>
+        </is>
+      </c>
+      <c r="P50">
+        <v>132440</v>
+      </c>
+      <c r="Q50">
+        <v>10.81</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Malabo</t>
+        </is>
+      </c>
+      <c r="S50">
+        <v>132440</v>
+      </c>
+      <c r="T50">
+        <v>10.81</v>
+      </c>
+      <c r="U50">
         <v>9</v>
       </c>
-      <c r="M49">
-        <v>9</v>
-      </c>
-      <c r="N49">
-        <v>3</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Vitoria-Gasteiz</t>
-        </is>
-      </c>
-      <c r="P49">
-        <v>260402</v>
-      </c>
-      <c r="Q49">
-        <v>11.61</v>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>Vitoria-Gasteiz</t>
-        </is>
-      </c>
-      <c r="S49">
-        <v>260402</v>
-      </c>
-      <c r="T49">
-        <v>11.61</v>
-      </c>
-      <c r="U49">
-        <v>7</v>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Álava</t>
-        </is>
-      </c>
-      <c r="X49">
-        <v>3038.0</v>
-      </c>
-      <c r="Y49">
-        <v>0.6</v>
-      </c>
-      <c r="Z49">
-        <v>41.99</v>
-      </c>
-      <c r="AA49">
-        <v>48</v>
-      </c>
-      <c r="AB49">
-        <v>1</v>
-      </c>
-      <c r="AC49">
-        <v>341961</v>
-      </c>
-      <c r="AD49">
-        <v>0.7</v>
-      </c>
-      <c r="AE49">
-        <v>15.25</v>
-      </c>
-      <c r="AF49">
-        <v>37</v>
-      </c>
-      <c r="AG49">
-        <v>3</v>
-      </c>
-      <c r="AH49">
-        <v>51</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Vitoria-Gasteiz</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>260402</v>
-      </c>
-      <c r="AK49">
-        <v>76.15</v>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>Vitoria-Gasteiz</t>
-        </is>
-      </c>
-      <c r="AM49">
-        <v>260402</v>
-      </c>
-      <c r="AN49">
-        <v>76.15</v>
-      </c>
-    </row>
-    <row r="50">
       <c r="V50" t="inlineStr">
         <is>
           <t>Provincia</t>
@@ -4426,63 +4505,66 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Bizkaia</t>
+          <t>Fernando Poo</t>
         </is>
       </c>
       <c r="X50">
-        <v>2217.0</v>
+        <v>2034.0</v>
       </c>
       <c r="Y50">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="Z50">
-        <v>30.64</v>
+        <v>7.25</v>
       </c>
       <c r="AA50">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="AB50">
         <v>2</v>
       </c>
       <c r="AC50">
-        <v>1167233</v>
+        <v>340362</v>
       </c>
       <c r="AD50">
-        <v>2.38</v>
+        <v>0.52</v>
       </c>
       <c r="AE50">
-        <v>52.05</v>
+        <v>27.78</v>
       </c>
       <c r="AF50">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="AG50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH50">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Bilbao</t>
+          <t>Malabo</t>
         </is>
       </c>
       <c r="AJ50">
-        <v>350975</v>
+        <v>132440</v>
       </c>
       <c r="AK50">
-        <v>30.07</v>
+        <v>38.91</v>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>Bilbao</t>
+          <t>Malabo</t>
         </is>
       </c>
       <c r="AM50">
-        <v>350975</v>
+        <v>132440</v>
       </c>
       <c r="AN50">
-        <v>30.07</v>
+        <v>38.91</v>
+      </c>
+      <c r="AO50">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -4493,66 +4575,1079 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Gipuzkoa</t>
+          <t>Rio Muni</t>
         </is>
       </c>
       <c r="X51">
+        <v>26017.0</v>
+      </c>
+      <c r="Y51">
+        <v>2.83</v>
+      </c>
+      <c r="Z51">
+        <v>92.75</v>
+      </c>
+      <c r="AA51">
+        <v>3</v>
+      </c>
+      <c r="AB51">
+        <v>1</v>
+      </c>
+      <c r="AC51">
+        <v>885015</v>
+      </c>
+      <c r="AD51">
+        <v>1.35</v>
+      </c>
+      <c r="AE51">
+        <v>72.22</v>
+      </c>
+      <c r="AF51">
+        <v>22</v>
+      </c>
+      <c r="AG51">
+        <v>1</v>
+      </c>
+      <c r="AH51">
+        <v>10</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Bata</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>132235</v>
+      </c>
+      <c r="AK51">
+        <v>14.94</v>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Bata</t>
+        </is>
+      </c>
+      <c r="AM51">
+        <v>132235</v>
+      </c>
+      <c r="AN51">
+        <v>14.94</v>
+      </c>
+      <c r="AO51">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Murcia</t>
+        </is>
+      </c>
+      <c r="F52">
+        <v>26239.0</v>
+      </c>
+      <c r="G52">
+        <v>2.85</v>
+      </c>
+      <c r="H52">
+        <v>12</v>
+      </c>
+      <c r="I52">
+        <v>12</v>
+      </c>
+      <c r="J52">
+        <v>1977740</v>
+      </c>
+      <c r="K52">
+        <v>3.02</v>
+      </c>
+      <c r="L52">
+        <v>12</v>
+      </c>
+      <c r="M52">
+        <v>12</v>
+      </c>
+      <c r="N52">
+        <v>2</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Murcia</t>
+        </is>
+      </c>
+      <c r="P52">
+        <v>477631</v>
+      </c>
+      <c r="Q52">
+        <v>24.15</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Murcia</t>
+        </is>
+      </c>
+      <c r="S52">
+        <v>477631</v>
+      </c>
+      <c r="T52">
+        <v>24.15</v>
+      </c>
+      <c r="U52">
+        <v>15</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="X52">
+        <v>14926.0</v>
+      </c>
+      <c r="Y52">
+        <v>1.62</v>
+      </c>
+      <c r="Z52">
+        <v>56.88</v>
+      </c>
+      <c r="AA52">
+        <v>14</v>
+      </c>
+      <c r="AB52">
+        <v>1</v>
+      </c>
+      <c r="AC52">
+        <v>390751</v>
+      </c>
+      <c r="AD52">
+        <v>0.6</v>
+      </c>
+      <c r="AE52">
+        <v>19.76</v>
+      </c>
+      <c r="AF52">
+        <v>42</v>
+      </c>
+      <c r="AG52">
+        <v>2</v>
+      </c>
+      <c r="AH52">
+        <v>87</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>175068</v>
+      </c>
+      <c r="AK52">
+        <v>44.8</v>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="AM52">
+        <v>175068</v>
+      </c>
+      <c r="AN52">
+        <v>44.8</v>
+      </c>
+      <c r="AO52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Murcia</t>
+        </is>
+      </c>
+      <c r="X53">
+        <v>11313.0</v>
+      </c>
+      <c r="Y53">
+        <v>1.23</v>
+      </c>
+      <c r="Z53">
+        <v>43.12</v>
+      </c>
+      <c r="AA53">
+        <v>25</v>
+      </c>
+      <c r="AB53">
+        <v>2</v>
+      </c>
+      <c r="AC53">
+        <v>1586989</v>
+      </c>
+      <c r="AD53">
+        <v>2.43</v>
+      </c>
+      <c r="AE53">
+        <v>80.24</v>
+      </c>
+      <c r="AF53">
+        <v>12</v>
+      </c>
+      <c r="AG53">
+        <v>1</v>
+      </c>
+      <c r="AH53">
+        <v>45</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Murcia</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>477631</v>
+      </c>
+      <c r="AK53">
+        <v>30.1</v>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Murcia</t>
+        </is>
+      </c>
+      <c r="AM53">
+        <v>477631</v>
+      </c>
+      <c r="AN53">
+        <v>30.1</v>
+      </c>
+      <c r="AO53">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
+      <c r="F54">
+        <v>10390.0</v>
+      </c>
+      <c r="G54">
+        <v>1.13</v>
+      </c>
+      <c r="H54">
+        <v>15</v>
+      </c>
+      <c r="I54">
+        <v>15</v>
+      </c>
+      <c r="J54">
+        <v>683854</v>
+      </c>
+      <c r="K54">
+        <v>1.05</v>
+      </c>
+      <c r="L54">
+        <v>19</v>
+      </c>
+      <c r="M54">
+        <v>19</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Pamplona</t>
+        </is>
+      </c>
+      <c r="P54">
+        <v>209676</v>
+      </c>
+      <c r="Q54">
+        <v>30.66</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Pamplona</t>
+        </is>
+      </c>
+      <c r="S54">
+        <v>209676</v>
+      </c>
+      <c r="T54">
+        <v>30.66</v>
+      </c>
+      <c r="U54">
+        <v>5</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Navarra</t>
+        </is>
+      </c>
+      <c r="X54">
+        <v>10390.0</v>
+      </c>
+      <c r="Y54">
+        <v>1.13</v>
+      </c>
+      <c r="Z54">
+        <v>100.0</v>
+      </c>
+      <c r="AA54">
+        <v>29</v>
+      </c>
+      <c r="AB54">
+        <v>1</v>
+      </c>
+      <c r="AC54">
+        <v>683854</v>
+      </c>
+      <c r="AD54">
+        <v>1.05</v>
+      </c>
+      <c r="AE54">
+        <v>100.0</v>
+      </c>
+      <c r="AF54">
+        <v>31</v>
+      </c>
+      <c r="AG54">
+        <v>1</v>
+      </c>
+      <c r="AH54">
+        <v>272</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Pamplona</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <v>209676</v>
+      </c>
+      <c r="AK54">
+        <v>30.66</v>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Pamplona</t>
+        </is>
+      </c>
+      <c r="AM54">
+        <v>209676</v>
+      </c>
+      <c r="AN54">
+        <v>30.66</v>
+      </c>
+      <c r="AO54">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="F55">
+        <v>8867.54</v>
+      </c>
+      <c r="G55">
+        <v>0.96</v>
+      </c>
+      <c r="H55">
+        <v>16</v>
+      </c>
+      <c r="I55">
+        <v>16</v>
+      </c>
+      <c r="J55">
+        <v>3285874</v>
+      </c>
+      <c r="K55">
+        <v>5.02</v>
+      </c>
+      <c r="L55">
+        <v>8</v>
+      </c>
+      <c r="M55">
+        <v>8</v>
+      </c>
+      <c r="N55">
+        <v>1</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>San Juan</t>
+        </is>
+      </c>
+      <c r="P55">
+        <v>329737</v>
+      </c>
+      <c r="Q55">
+        <v>10.03</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>San Juan</t>
+        </is>
+      </c>
+      <c r="S55">
+        <v>329737</v>
+      </c>
+      <c r="T55">
+        <v>10.03</v>
+      </c>
+      <c r="U55">
+        <v>26</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="X55">
+        <v>8867.54</v>
+      </c>
+      <c r="Y55">
+        <v>0.96</v>
+      </c>
+      <c r="Z55">
+        <v>100.0</v>
+      </c>
+      <c r="AA55">
+        <v>33</v>
+      </c>
+      <c r="AB55">
+        <v>1</v>
+      </c>
+      <c r="AC55">
+        <v>3285874</v>
+      </c>
+      <c r="AD55">
+        <v>5.02</v>
+      </c>
+      <c r="AE55">
+        <v>100.0</v>
+      </c>
+      <c r="AF55">
+        <v>4</v>
+      </c>
+      <c r="AG55">
+        <v>1</v>
+      </c>
+      <c r="AH55">
+        <v>78</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>San Juan</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <v>329737</v>
+      </c>
+      <c r="AK55">
+        <v>10.03</v>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>San Juan</t>
+        </is>
+      </c>
+      <c r="AM55">
+        <v>329737</v>
+      </c>
+      <c r="AN55">
+        <v>10.03</v>
+      </c>
+      <c r="AO55">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F56">
+        <v>23255.0</v>
+      </c>
+      <c r="G56">
+        <v>2.53</v>
+      </c>
+      <c r="H56">
+        <v>13</v>
+      </c>
+      <c r="I56">
+        <v>13</v>
+      </c>
+      <c r="J56">
+        <v>5425182</v>
+      </c>
+      <c r="K56">
+        <v>8.29</v>
+      </c>
+      <c r="L56">
+        <v>4</v>
+      </c>
+      <c r="M56">
+        <v>4</v>
+      </c>
+      <c r="N56">
+        <v>3</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>València</t>
+        </is>
+      </c>
+      <c r="P56">
+        <v>841558</v>
+      </c>
+      <c r="Q56">
+        <v>15.51</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>València</t>
+        </is>
+      </c>
+      <c r="S56">
+        <v>841558</v>
+      </c>
+      <c r="T56">
+        <v>15.51</v>
+      </c>
+      <c r="U56">
+        <v>41</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="X56">
+        <v>5817.0</v>
+      </c>
+      <c r="Y56">
+        <v>0.63</v>
+      </c>
+      <c r="Z56">
+        <v>25.01</v>
+      </c>
+      <c r="AA56">
+        <v>51</v>
+      </c>
+      <c r="AB56">
+        <v>3</v>
+      </c>
+      <c r="AC56">
+        <v>2033566</v>
+      </c>
+      <c r="AD56">
+        <v>3.11</v>
+      </c>
+      <c r="AE56">
+        <v>37.48</v>
+      </c>
+      <c r="AF56">
+        <v>8</v>
+      </c>
+      <c r="AG56">
+        <v>2</v>
+      </c>
+      <c r="AH56">
+        <v>141</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>2033566</v>
+      </c>
+      <c r="AK56">
+        <v>100.0</v>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Alacant</t>
+        </is>
+      </c>
+      <c r="AM56">
+        <v>365586</v>
+      </c>
+      <c r="AN56">
+        <v>17.98</v>
+      </c>
+      <c r="AO56">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="X57">
+        <v>6632.0</v>
+      </c>
+      <c r="Y57">
+        <v>0.72</v>
+      </c>
+      <c r="Z57">
+        <v>28.52</v>
+      </c>
+      <c r="AA57">
+        <v>48</v>
+      </c>
+      <c r="AB57">
+        <v>2</v>
+      </c>
+      <c r="AC57">
+        <v>627620</v>
+      </c>
+      <c r="AD57">
+        <v>0.96</v>
+      </c>
+      <c r="AE57">
+        <v>11.57</v>
+      </c>
+      <c r="AF57">
+        <v>34</v>
+      </c>
+      <c r="AG57">
+        <v>3</v>
+      </c>
+      <c r="AH57">
+        <v>135</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Castelló de la Plana</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>183709</v>
+      </c>
+      <c r="AK57">
+        <v>29.27</v>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Castelló de la Plana</t>
+        </is>
+      </c>
+      <c r="AM57">
+        <v>183709</v>
+      </c>
+      <c r="AN57">
+        <v>29.27</v>
+      </c>
+      <c r="AO57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="X58">
+        <v>10806.0</v>
+      </c>
+      <c r="Y58">
+        <v>1.17</v>
+      </c>
+      <c r="Z58">
+        <v>46.47</v>
+      </c>
+      <c r="AA58">
+        <v>26</v>
+      </c>
+      <c r="AB58">
+        <v>1</v>
+      </c>
+      <c r="AC58">
+        <v>2763996</v>
+      </c>
+      <c r="AD58">
+        <v>4.22</v>
+      </c>
+      <c r="AE58">
+        <v>50.95</v>
+      </c>
+      <c r="AF58">
+        <v>6</v>
+      </c>
+      <c r="AG58">
+        <v>1</v>
+      </c>
+      <c r="AH58">
+        <v>266</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>València</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>841558</v>
+      </c>
+      <c r="AK58">
+        <v>30.45</v>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>València</t>
+        </is>
+      </c>
+      <c r="AM58">
+        <v>841558</v>
+      </c>
+      <c r="AN58">
+        <v>30.45</v>
+      </c>
+      <c r="AO58">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Regiones Vascongadas</t>
+        </is>
+      </c>
+      <c r="F59">
+        <v>7235.0</v>
+      </c>
+      <c r="G59">
+        <v>0.79</v>
+      </c>
+      <c r="H59">
+        <v>18</v>
+      </c>
+      <c r="I59">
+        <v>18</v>
+      </c>
+      <c r="J59">
+        <v>2242343</v>
+      </c>
+      <c r="K59">
+        <v>3.43</v>
+      </c>
+      <c r="L59">
+        <v>11</v>
+      </c>
+      <c r="M59">
+        <v>11</v>
+      </c>
+      <c r="N59">
+        <v>3</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="P59">
+        <v>260402</v>
+      </c>
+      <c r="Q59">
+        <v>11.61</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="S59">
+        <v>260402</v>
+      </c>
+      <c r="T59">
+        <v>11.61</v>
+      </c>
+      <c r="U59">
+        <v>16</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Álava</t>
+        </is>
+      </c>
+      <c r="X59">
+        <v>3038.0</v>
+      </c>
+      <c r="Y59">
+        <v>0.33</v>
+      </c>
+      <c r="Z59">
+        <v>41.99</v>
+      </c>
+      <c r="AA59">
+        <v>56</v>
+      </c>
+      <c r="AB59">
+        <v>1</v>
+      </c>
+      <c r="AC59">
+        <v>341961</v>
+      </c>
+      <c r="AD59">
+        <v>0.52</v>
+      </c>
+      <c r="AE59">
+        <v>15.25</v>
+      </c>
+      <c r="AF59">
+        <v>45</v>
+      </c>
+      <c r="AG59">
+        <v>3</v>
+      </c>
+      <c r="AH59">
+        <v>51</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="AJ59">
+        <v>260402</v>
+      </c>
+      <c r="AK59">
+        <v>76.15</v>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Vitoria-Gasteiz</t>
+        </is>
+      </c>
+      <c r="AM59">
+        <v>260402</v>
+      </c>
+      <c r="AN59">
+        <v>76.15</v>
+      </c>
+      <c r="AO59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Guipúzcoa</t>
+        </is>
+      </c>
+      <c r="X60">
         <v>1980.0</v>
       </c>
-      <c r="Y51">
-        <v>0.39</v>
-      </c>
-      <c r="Z51">
+      <c r="Y60">
+        <v>0.22</v>
+      </c>
+      <c r="Z60">
         <v>27.37</v>
       </c>
-      <c r="AA51">
-        <v>50</v>
-      </c>
-      <c r="AB51">
+      <c r="AA60">
+        <v>59</v>
+      </c>
+      <c r="AB60">
         <v>3</v>
       </c>
-      <c r="AC51">
+      <c r="AC60">
         <v>733149</v>
       </c>
-      <c r="AD51">
-        <v>1.49</v>
-      </c>
-      <c r="AE51">
+      <c r="AD60">
+        <v>1.12</v>
+      </c>
+      <c r="AE60">
         <v>32.7</v>
       </c>
-      <c r="AF51">
-        <v>23</v>
-      </c>
-      <c r="AG51">
+      <c r="AF60">
+        <v>29</v>
+      </c>
+      <c r="AG60">
         <v>2</v>
       </c>
-      <c r="AH51">
+      <c r="AH60">
         <v>88</v>
       </c>
-      <c r="AI51" t="inlineStr">
+      <c r="AI60" t="inlineStr">
         <is>
           <t>Donostia</t>
         </is>
       </c>
-      <c r="AJ51">
+      <c r="AJ60">
         <v>189507</v>
       </c>
-      <c r="AK51">
+      <c r="AK60">
         <v>25.85</v>
       </c>
-      <c r="AL51" t="inlineStr">
+      <c r="AL60" t="inlineStr">
         <is>
           <t>Donostia</t>
         </is>
       </c>
-      <c r="AM51">
+      <c r="AM60">
         <v>189507</v>
       </c>
-      <c r="AN51">
+      <c r="AN60">
         <v>25.85</v>
       </c>
+      <c r="AO60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vizcaya</t>
+        </is>
+      </c>
+      <c r="X61">
+        <v>2217.0</v>
+      </c>
+      <c r="Y61">
+        <v>0.24</v>
+      </c>
+      <c r="Z61">
+        <v>30.64</v>
+      </c>
+      <c r="AA61">
+        <v>57</v>
+      </c>
+      <c r="AB61">
+        <v>2</v>
+      </c>
+      <c r="AC61">
+        <v>1167233</v>
+      </c>
+      <c r="AD61">
+        <v>1.78</v>
+      </c>
+      <c r="AE61">
+        <v>52.05</v>
+      </c>
+      <c r="AF61">
+        <v>16</v>
+      </c>
+      <c r="AG61">
+        <v>1</v>
+      </c>
+      <c r="AH61">
+        <v>113</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Bilbao</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>350975</v>
+      </c>
+      <c r="AK61">
+        <v>30.07</v>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Bilbao</t>
+        </is>
+      </c>
+      <c r="AM61">
+        <v>350975</v>
+      </c>
+      <c r="AN61">
+        <v>30.07</v>
+      </c>
+      <c r="AO61">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO51"/>
+  <autoFilter ref="A1:AO61"/>
 </worksheet>
 </file>